--- a/kirana_store_tracker.xlsx
+++ b/kirana_store_tracker.xlsx
@@ -1,20 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhis\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B7C2F8F-5CD0-41D7-94E7-248372BFA9E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="10170" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Raw_Data" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="Category_Summary" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="README" sheetId="1" r:id="rId1"/>
+    <sheet name="Dashboard" sheetId="2" r:id="rId2"/>
+    <sheet name="Raw_Data" sheetId="3" r:id="rId3"/>
+    <sheet name="Category_Summary" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -25,323 +39,321 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="101">
   <si>
-    <t xml:space="preserve">Kirana Store Reorder &amp; Wastage Tracker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Project Objective</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A small kirana (grocery) store owner cannot see, at a glance, which products are about to run out of stock or which categories are losing the most money to wastage (spoilage, damage, expiry). This workbook turns raw daily stock data into a live dashboard that answers both questions automatically.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sheets in this Workbook</t>
-  </si>
-  <si>
-    <t xml:space="preserve">- Dashboard - KPI cards, Top 10 products chart, wastage % by category chart.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">- Raw_Data - 43 products, 6 categories, input data (blue font) and calculated columns (black font).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">- Category_Summary - SUMIFS-based rollup of sales, wastage and wastage % by category.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Key Formulas Used</t>
-  </si>
-  <si>
-    <t xml:space="preserve">- Closing Stock:  =Opening Stock + Purchased Qty - Sold Qty - Wastage Qty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">- Reorder Status:  =IF(Closing Stock &lt; Reorder Level, "Reorder Now", "OK")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">- Wastage %:  =IFERROR(Wastage Qty / (Sold Qty + Wastage Qty), 0)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">- Total Sales Value:  =Sold Qty * Selling Price</t>
-  </si>
-  <si>
-    <t xml:space="preserve">- Total Wastage Value:  =Wastage Qty * Purchase Price</t>
-  </si>
-  <si>
-    <t xml:space="preserve">- Sales Rank:  =RANK(Total Sales Value, range, 0)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">- Category Rollups:  =SUMIFS(value_range, category_range, category_name)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">- Top 10 Product Lookup:  =INDEX(name_range, MATCH(rank_number, rank_range, 0))</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Color Legend</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blue font = hardcoded input data.   Black font = formula-driven calculated value.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Red highlight = product needs reorder.   Green highlight = stock is healthy.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Note on Data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Product, price and quantity data is simulated for portfolio/practice purposes (not from a real store). Structure and formula logic reflect how a real kirana store's inventory sheet would be built.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kirana Store Reorder &amp; Wastage Dashboard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Inventory, sales and wastage snapshot across 43 products in 6 categories</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total Revenue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total Wastage Cost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Overall Wastage %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Products to Reorder</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Top 10 Products by Sales Value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Products Needing Reorder</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Product Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sales Value (Rs)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Closing Stock</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reorder Level</t>
-  </si>
-  <si>
-    <t xml:space="preserve">See 'Raw_Data' sheet, column L (Reorder Status).
+    <t>Kirana Store Reorder &amp; Wastage Tracker</t>
+  </si>
+  <si>
+    <t>Project Objective</t>
+  </si>
+  <si>
+    <t>A small kirana (grocery) store owner cannot see, at a glance, which products are about to run out of stock or which categories are losing the most money to wastage (spoilage, damage, expiry). This workbook turns raw daily stock data into a live dashboard that answers both questions automatically.</t>
+  </si>
+  <si>
+    <t>Sheets in this Workbook</t>
+  </si>
+  <si>
+    <t>- Dashboard - KPI cards, Top 10 products chart, wastage % by category chart.</t>
+  </si>
+  <si>
+    <t>- Raw_Data - 43 products, 6 categories, input data (blue font) and calculated columns (black font).</t>
+  </si>
+  <si>
+    <t>- Category_Summary - SUMIFS-based rollup of sales, wastage and wastage % by category.</t>
+  </si>
+  <si>
+    <t>Key Formulas Used</t>
+  </si>
+  <si>
+    <t>- Closing Stock:  =Opening Stock + Purchased Qty - Sold Qty - Wastage Qty</t>
+  </si>
+  <si>
+    <t>- Reorder Status:  =IF(Closing Stock &lt; Reorder Level, "Reorder Now", "OK")</t>
+  </si>
+  <si>
+    <t>- Wastage %:  =IFERROR(Wastage Qty / (Sold Qty + Wastage Qty), 0)</t>
+  </si>
+  <si>
+    <t>- Total Sales Value:  =Sold Qty * Selling Price</t>
+  </si>
+  <si>
+    <t>- Total Wastage Value:  =Wastage Qty * Purchase Price</t>
+  </si>
+  <si>
+    <t>- Sales Rank:  =RANK(Total Sales Value, range, 0)</t>
+  </si>
+  <si>
+    <t>- Category Rollups:  =SUMIFS(value_range, category_range, category_name)</t>
+  </si>
+  <si>
+    <t>- Top 10 Product Lookup:  =INDEX(name_range, MATCH(rank_number, rank_range, 0))</t>
+  </si>
+  <si>
+    <t>Color Legend</t>
+  </si>
+  <si>
+    <t>Blue font = hardcoded input data.   Black font = formula-driven calculated value.</t>
+  </si>
+  <si>
+    <t>Red highlight = product needs reorder.   Green highlight = stock is healthy.</t>
+  </si>
+  <si>
+    <t>Note on Data</t>
+  </si>
+  <si>
+    <t>Product, price and quantity data is simulated for portfolio/practice purposes (not from a real store). Structure and formula logic reflect how a real kirana store's inventory sheet would be built.</t>
+  </si>
+  <si>
+    <t>Kirana Store Reorder &amp; Wastage Dashboard</t>
+  </si>
+  <si>
+    <t>Inventory, sales and wastage snapshot across 43 products in 6 categories</t>
+  </si>
+  <si>
+    <t>Total Revenue</t>
+  </si>
+  <si>
+    <t>Total Wastage Cost</t>
+  </si>
+  <si>
+    <t>Overall Wastage %</t>
+  </si>
+  <si>
+    <t>Products to Reorder</t>
+  </si>
+  <si>
+    <t>Top 10 Products by Sales Value</t>
+  </si>
+  <si>
+    <t>Products Needing Reorder</t>
+  </si>
+  <si>
+    <t>Rank</t>
+  </si>
+  <si>
+    <t>Product Name</t>
+  </si>
+  <si>
+    <t>Sales Value (Rs)</t>
+  </si>
+  <si>
+    <t>Closing Stock</t>
+  </si>
+  <si>
+    <t>Reorder Level</t>
+  </si>
+  <si>
+    <t>See 'Raw_Data' sheet, column L (Reorder Status).
 Filter that column to 'Reorder Now' to see the exact list.
 Count of items needing reorder is shown in the KPI card above.</t>
   </si>
   <si>
-    <t xml:space="preserve">Product ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Category</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Purchase Price (Rs)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Selling Price (Rs)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Opening Stock</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Purchased Qty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sold Qty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wastage Qty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reorder Status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wastage %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Profit per Unit (Rs)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total Sales Value (Rs)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total Wastage Value (Rs)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sales Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toned Milk 500ml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dairy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Full Cream Milk 1L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Curd 400g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paneer 200g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Butter 100g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cheese Slices 200g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ghee 500ml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aloo Bhujia 200g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Snacks &amp; Namkeen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Potato Chips 100g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mixture 250g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Banana Chips 150g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Salted Peanuts 200g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sev 200g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Namkeen Mix 500g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cola 750ml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beverages</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Orange Juice 1L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mineral Water 1L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lemon Drink 500ml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tea Powder 250g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Instant Coffee 100g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Energy Drink 250ml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Basmati Rice 5kg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grocery &amp; Staples</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wheat Flour 5kg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toor Dal 1kg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sugar 1kg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cooking Oil 1L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Salt 1kg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Besan 500g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Poha 500g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shampoo 200ml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Personal Care</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toothpaste 150g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Soap Bar 100g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hair Oil 200ml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Face Wash 100ml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Talcum Powder 100g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Razor Pack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Detergent Powder 1kg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Household Items</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dish Wash Bar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Floor Cleaner 1L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toilet Cleaner 500ml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Room Freshener</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Broom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Garbage Bags Pack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total Sold Qty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total Wastage Qty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOTAL</t>
+    <t>Product ID</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Purchase Price (Rs)</t>
+  </si>
+  <si>
+    <t>Selling Price (Rs)</t>
+  </si>
+  <si>
+    <t>Opening Stock</t>
+  </si>
+  <si>
+    <t>Purchased Qty</t>
+  </si>
+  <si>
+    <t>Sold Qty</t>
+  </si>
+  <si>
+    <t>Wastage Qty</t>
+  </si>
+  <si>
+    <t>Reorder Status</t>
+  </si>
+  <si>
+    <t>Wastage %</t>
+  </si>
+  <si>
+    <t>Profit per Unit (Rs)</t>
+  </si>
+  <si>
+    <t>Total Sales Value (Rs)</t>
+  </si>
+  <si>
+    <t>Total Wastage Value (Rs)</t>
+  </si>
+  <si>
+    <t>Sales Rank</t>
+  </si>
+  <si>
+    <t>Toned Milk 500ml</t>
+  </si>
+  <si>
+    <t>Dairy</t>
+  </si>
+  <si>
+    <t>Full Cream Milk 1L</t>
+  </si>
+  <si>
+    <t>Curd 400g</t>
+  </si>
+  <si>
+    <t>Paneer 200g</t>
+  </si>
+  <si>
+    <t>Butter 100g</t>
+  </si>
+  <si>
+    <t>Cheese Slices 200g</t>
+  </si>
+  <si>
+    <t>Ghee 500ml</t>
+  </si>
+  <si>
+    <t>Aloo Bhujia 200g</t>
+  </si>
+  <si>
+    <t>Snacks &amp; Namkeen</t>
+  </si>
+  <si>
+    <t>Potato Chips 100g</t>
+  </si>
+  <si>
+    <t>Mixture 250g</t>
+  </si>
+  <si>
+    <t>Banana Chips 150g</t>
+  </si>
+  <si>
+    <t>Salted Peanuts 200g</t>
+  </si>
+  <si>
+    <t>Sev 200g</t>
+  </si>
+  <si>
+    <t>Namkeen Mix 500g</t>
+  </si>
+  <si>
+    <t>Cola 750ml</t>
+  </si>
+  <si>
+    <t>Beverages</t>
+  </si>
+  <si>
+    <t>Orange Juice 1L</t>
+  </si>
+  <si>
+    <t>Mineral Water 1L</t>
+  </si>
+  <si>
+    <t>Lemon Drink 500ml</t>
+  </si>
+  <si>
+    <t>Tea Powder 250g</t>
+  </si>
+  <si>
+    <t>Instant Coffee 100g</t>
+  </si>
+  <si>
+    <t>Energy Drink 250ml</t>
+  </si>
+  <si>
+    <t>Basmati Rice 5kg</t>
+  </si>
+  <si>
+    <t>Grocery &amp; Staples</t>
+  </si>
+  <si>
+    <t>Wheat Flour 5kg</t>
+  </si>
+  <si>
+    <t>Toor Dal 1kg</t>
+  </si>
+  <si>
+    <t>Sugar 1kg</t>
+  </si>
+  <si>
+    <t>Cooking Oil 1L</t>
+  </si>
+  <si>
+    <t>Salt 1kg</t>
+  </si>
+  <si>
+    <t>Besan 500g</t>
+  </si>
+  <si>
+    <t>Poha 500g</t>
+  </si>
+  <si>
+    <t>Shampoo 200ml</t>
+  </si>
+  <si>
+    <t>Personal Care</t>
+  </si>
+  <si>
+    <t>Toothpaste 150g</t>
+  </si>
+  <si>
+    <t>Soap Bar 100g</t>
+  </si>
+  <si>
+    <t>Hair Oil 200ml</t>
+  </si>
+  <si>
+    <t>Face Wash 100ml</t>
+  </si>
+  <si>
+    <t>Talcum Powder 100g</t>
+  </si>
+  <si>
+    <t>Razor Pack</t>
+  </si>
+  <si>
+    <t>Detergent Powder 1kg</t>
+  </si>
+  <si>
+    <t>Household Items</t>
+  </si>
+  <si>
+    <t>Dish Wash Bar</t>
+  </si>
+  <si>
+    <t>Floor Cleaner 1L</t>
+  </si>
+  <si>
+    <t>Toilet Cleaner 500ml</t>
+  </si>
+  <si>
+    <t>Room Freshener</t>
+  </si>
+  <si>
+    <t>Broom</t>
+  </si>
+  <si>
+    <t>Garbage Bags Pack</t>
+  </si>
+  <si>
+    <t>Total Sold Qty</t>
+  </si>
+  <si>
+    <t>Total Wastage Qty</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="&quot;Rs &quot;#,##0"/>
-    <numFmt numFmtId="166" formatCode="0.0%"/>
-    <numFmt numFmtId="167" formatCode="0"/>
-    <numFmt numFmtId="168" formatCode="&quot;Rs &quot;#,##0.00"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="&quot;Rs &quot;#,##0"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="&quot;Rs &quot;#,##0.00"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -350,130 +362,83 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
+      <b/>
       <sz val="16"/>
       <color rgb="FF2E5395"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="12"/>
       <color rgb="FF2E5395"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10.5"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="18"/>
       <color rgb="FF2E5395"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <i val="true"/>
+      <i/>
       <sz val="10"/>
       <color rgb="FF808080"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="20"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <i val="true"/>
+      <i/>
       <sz val="10"/>
       <color rgb="FF595959"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="18"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -516,14 +481,14 @@
     </fill>
   </fills>
   <borders count="2">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left style="thin">
         <color rgb="FFBFBFBF"/>
       </left>
@@ -539,158 +504,82 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="29">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="1" fontId="7" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="165" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="18" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="12" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="12" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
   <dxfs count="2">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -701,17 +590,8 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -770,15 +650,33 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF2E5395"/>
       <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
+  <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
@@ -787,7 +685,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="1" sz="1800" spc="-1" strike="noStrike">
+              <a:defRPr sz="1800" b="1" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -795,7 +693,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr b="1" sz="1800" spc="-1" strike="noStrike">
+              <a:rPr lang="en-IN" sz="1800" b="1" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -816,6 +714,7 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
+      <c:layout/>
       <c:barChart>
         <c:barDir val="col"/>
         <c:grouping val="clustered"/>
@@ -825,7 +724,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Category_Summary!F1</c:f>
+              <c:f>Category_Summary!$F$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -836,7 +735,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="4f81bd"/>
+              <a:srgbClr val="4F81BD"/>
             </a:solidFill>
             <a:ln w="0">
               <a:noFill/>
@@ -844,18 +743,26 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="square"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
                     <a:latin typeface="Calibri"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:txPr>
             <c:dLblPos val="outEnd"/>
@@ -864,8 +771,9 @@
             <c:showCatName val="1"/>
             <c:showSerName val="1"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator>; </c:separator>
-            <c:showLeaderLines val="1"/>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
@@ -905,29 +813,41 @@
                 <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0.153256704980843</c:v>
+                  <c:v>0.1532567049808429</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.0617142857142857</c:v>
+                  <c:v>6.1714285714285715E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.0464135021097046</c:v>
+                  <c:v>4.6413502109704644E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.0494117647058824</c:v>
+                  <c:v>4.9411764705882349E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.046286329386437</c:v>
+                  <c:v>4.6286329386437029E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.0275974025974026</c:v>
+                  <c:v>2.7597402597402596E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-26DA-4EDD-B5C3-07A4985213C5}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:overlap val="0"/>
         <c:axId val="73186208"/>
         <c:axId val="81336255"/>
       </c:barChart>
@@ -945,7 +865,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="1" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="1" strike="noStrike" spc="-1">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
@@ -953,7 +873,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr b="1" sz="1000" spc="-1" strike="noStrike">
+                  <a:rPr lang="en-IN" sz="1000" b="1" strike="noStrike" spc="-1">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
@@ -989,13 +909,14 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="81336255"/>
@@ -1029,7 +950,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="1" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="1" strike="noStrike" spc="-1">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
@@ -1037,7 +958,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr b="1" sz="1000" spc="-1" strike="noStrike">
+                  <a:rPr lang="en-IN" sz="1000" b="1" strike="noStrike" spc="-1">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
@@ -1073,13 +994,14 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="73186208"/>
@@ -1095,25 +1017,33 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="1"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:srgbClr val="ffffff"/>
+      <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
     <a:ln w="9360">
       <a:solidFill>
-        <a:srgbClr val="d9d9d9"/>
+        <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
       <a:round/>
     </a:ln>
   </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
+  <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
@@ -1122,7 +1052,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="1" sz="1800" spc="-1" strike="noStrike">
+              <a:defRPr sz="1800" b="1" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -1130,7 +1060,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr b="1" sz="1800" spc="-1" strike="noStrike">
+              <a:rPr lang="en-IN" sz="1800" b="1" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -1151,6 +1081,7 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
+      <c:layout/>
       <c:barChart>
         <c:barDir val="bar"/>
         <c:grouping val="clustered"/>
@@ -1160,7 +1091,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Dashboard!D11</c:f>
+              <c:f>Dashboard!$D$11</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1171,7 +1102,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="4f81bd"/>
+              <a:srgbClr val="4F81BD"/>
             </a:solidFill>
             <a:ln w="0">
               <a:noFill/>
@@ -1179,15 +1110,23 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -1195,8 +1134,9 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator> </c:separator>
-            <c:showLeaderLines val="1"/>
+            <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
@@ -1257,10 +1197,10 @@
                   <c:v>53844.21</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>51074.24</c:v>
+                  <c:v>51074.239999999998</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>49332.48</c:v>
+                  <c:v>49332.479999999996</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>47573.75</c:v>
@@ -1272,7 +1212,7 @@
                   <c:v>42666.78</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>36277.6</c:v>
+                  <c:v>36277.600000000006</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>34979.1</c:v>
@@ -1280,9 +1220,21 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-E56E-476E-8FEF-905DA380EEDF}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:overlap val="0"/>
         <c:axId val="48718767"/>
         <c:axId val="21842095"/>
       </c:barChart>
@@ -1292,7 +1244,7 @@
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
-        <c:axPos val="b"/>
+        <c:axPos val="l"/>
         <c:title>
           <c:tx>
             <c:rich>
@@ -1300,7 +1252,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="1" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="1" strike="noStrike" spc="-1">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
@@ -1308,7 +1260,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr b="1" sz="1000" spc="-1" strike="noStrike">
+                  <a:rPr lang="en-IN" sz="1000" b="1" strike="noStrike" spc="-1">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
@@ -1344,13 +1296,14 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="21842095"/>
@@ -1366,7 +1319,7 @@
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
-        <c:axPos val="l"/>
+        <c:axPos val="b"/>
         <c:majorGridlines>
           <c:spPr>
             <a:ln w="9360">
@@ -1384,7 +1337,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="1" sz="1000" spc="-1" strike="noStrike">
+                  <a:defRPr sz="1000" b="1" strike="noStrike" spc="-1">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
@@ -1392,7 +1345,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr b="1" sz="1000" spc="-1" strike="noStrike">
+                  <a:rPr lang="en-IN" sz="1000" b="1" strike="noStrike" spc="-1">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
@@ -1428,13 +1381,14 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="48718767"/>
@@ -1450,23 +1404,29 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="1"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:srgbClr val="ffffff"/>
+      <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
     <a:ln w="9360">
       <a:solidFill>
-        <a:srgbClr val="d9d9d9"/>
+        <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
       <a:round/>
     </a:ln>
   </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
@@ -1475,19 +1435,25 @@
       <xdr:rowOff>100800</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>1107360</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>123120</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>63500</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>69850</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="0" name="Chart 1"/>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="211320" y="4638600"/>
-        <a:ext cx="5759640" cy="2879640"/>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1505,19 +1471,25 @@
       <xdr:rowOff>100800</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>1107360</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>584200</xdr:colOff>
       <xdr:row>58</xdr:row>
-      <xdr:rowOff>81000</xdr:rowOff>
+      <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="1" name="Chart 2"/>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="211320" y="7877160"/>
-        <a:ext cx="5759640" cy="3599640"/>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1531,41 +1503,41 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -1573,12 +1545,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -1607,7 +1579,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -1628,7 +1600,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -1679,7 +1651,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -1697,449 +1669,432 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:B27"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="100"/>
+    <col min="1" max="1" width="2" customWidth="1"/>
+    <col min="2" max="2" width="100" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+    <row r="2" spans="2:2" ht="20" x14ac:dyDescent="0.4">
+      <c r="B2" s="12" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="2" t="s">
+    <row r="4" spans="2:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B4" s="13" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="3" t="s">
+    <row r="5" spans="2:2" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="14" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="2" t="s">
+    <row r="7" spans="2:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B7" s="13" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="4" t="s">
+    <row r="8" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B8" s="15" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="4" t="s">
+    <row r="9" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B9" s="15" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="4" t="s">
+    <row r="10" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B10" s="15" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="2" t="s">
+    <row r="12" spans="2:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B12" s="13" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="4" t="s">
+    <row r="13" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B13" s="15" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="4" t="s">
+    <row r="14" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B14" s="15" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="4" t="s">
+    <row r="15" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B15" s="15" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="4" t="s">
+    <row r="16" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B16" s="15" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="4" t="s">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B17" s="15" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="4" t="s">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B18" s="15" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="4" t="s">
+    <row r="19" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B19" s="15" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="4" t="s">
+    <row r="20" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B20" s="15" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="2" t="s">
+    <row r="22" spans="2:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B22" s="13" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="4" t="s">
+    <row r="23" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B23" s="15" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="4" t="s">
+    <row r="24" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B24" s="15" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="2" t="s">
+    <row r="26" spans="2:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B26" s="13" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="5" t="s">
+    <row r="27" spans="2:2" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B27" s="16" t="s">
         <v>20</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B2:I21"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="7" style="0" width="14"/>
+    <col min="1" max="1" width="3" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="4" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="9" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="22.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="6" t="s">
+    <row r="2" spans="2:9" ht="23" x14ac:dyDescent="0.5">
+      <c r="B2" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="7" t="s">
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="11"/>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B3" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-    </row>
-    <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="8" t="s">
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+    </row>
+    <row r="5" spans="2:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="9" t="s">
+      <c r="C5" s="9"/>
+      <c r="D5" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E5" s="9"/>
-      <c r="F5" s="10" t="s">
+      <c r="E5" s="8"/>
+      <c r="F5" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="G5" s="10"/>
-      <c r="H5" s="11" t="s">
+      <c r="G5" s="7"/>
+      <c r="H5" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="I5" s="11"/>
-    </row>
-    <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="12" t="n">
-        <f aca="false">SUM(Raw_Data!O2:O44)</f>
+      <c r="I5" s="6"/>
+    </row>
+    <row r="6" spans="2:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B6" s="5">
+        <f>SUM(Raw_Data!O2:O44)</f>
         <v>1079244.71</v>
       </c>
-      <c r="C6" s="12"/>
-      <c r="D6" s="13" t="n">
-        <f aca="false">SUM(Raw_Data!P2:P44)</f>
-        <v>53446.52</v>
-      </c>
-      <c r="E6" s="13"/>
-      <c r="F6" s="14" t="n">
-        <f aca="false">SUM(Raw_Data!I2:I44)/(SUM(Raw_Data!H2:H44)+SUM(Raw_Data!I2:I44))</f>
-        <v>0.0639872025594881</v>
-      </c>
-      <c r="G6" s="14"/>
-      <c r="H6" s="15" t="n">
-        <f aca="false">COUNTIF(Raw_Data!L2:L44,"Reorder Now")</f>
+      <c r="C6" s="5"/>
+      <c r="D6" s="4">
+        <f>SUM(Raw_Data!P2:P44)</f>
+        <v>53446.520000000004</v>
+      </c>
+      <c r="E6" s="4"/>
+      <c r="F6" s="3">
+        <f>SUM(Raw_Data!I2:I44)/(SUM(Raw_Data!H2:H44)+SUM(Raw_Data!I2:I44))</f>
+        <v>6.3987202559488102E-2</v>
+      </c>
+      <c r="G6" s="3"/>
+      <c r="H6" s="2">
+        <f>COUNTIF(Raw_Data!L2:L44,"Reorder Now")</f>
         <v>21</v>
       </c>
-      <c r="I6" s="15"/>
-    </row>
-    <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="12"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="15"/>
-      <c r="I7" s="15"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="2" t="s">
+      <c r="I6" s="2"/>
+    </row>
+    <row r="7" spans="2:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+    </row>
+    <row r="10" spans="2:9" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B10" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F10" s="13" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="16" t="s">
+    <row r="11" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B11" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="16" t="s">
+      <c r="C11" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="D11" s="16" t="s">
+      <c r="D11" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="F11" s="16" t="s">
+      <c r="F11" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="G11" s="16" t="s">
+      <c r="G11" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="H11" s="16" t="s">
+      <c r="H11" s="17" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="17" t="n">
+    <row r="12" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="18">
         <v>1</v>
       </c>
-      <c r="C12" s="17" t="str">
-        <f aca="false">INDEX(Raw_Data!$B$2:$B$44,MATCH(B12,Raw_Data!$Q$2:$Q$44,0))</f>
+      <c r="C12" s="18" t="str">
+        <f>INDEX(Raw_Data!$B$2:$B$44,MATCH(B12,Raw_Data!$Q$2:$Q$44,0))</f>
         <v>Namkeen Mix 500g</v>
       </c>
-      <c r="D12" s="18" t="n">
-        <f aca="false">INDEX(Raw_Data!$O$2:$O$44,MATCH(B12,Raw_Data!$Q$2:$Q$44,0))</f>
+      <c r="D12" s="19">
+        <f>INDEX(Raw_Data!$O$2:$O$44,MATCH(B12,Raw_Data!$Q$2:$Q$44,0))</f>
         <v>67372.2</v>
       </c>
-      <c r="F12" s="19" t="s">
+      <c r="F12" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="G12" s="19"/>
-      <c r="H12" s="19"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="17" t="n">
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+    </row>
+    <row r="13" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B13" s="18">
         <v>2</v>
       </c>
-      <c r="C13" s="17" t="str">
-        <f aca="false">INDEX(Raw_Data!$B$2:$B$44,MATCH(B13,Raw_Data!$Q$2:$Q$44,0))</f>
+      <c r="C13" s="18" t="str">
+        <f>INDEX(Raw_Data!$B$2:$B$44,MATCH(B13,Raw_Data!$Q$2:$Q$44,0))</f>
         <v>Hair Oil 200ml</v>
       </c>
-      <c r="D13" s="18" t="n">
-        <f aca="false">INDEX(Raw_Data!$O$2:$O$44,MATCH(B13,Raw_Data!$Q$2:$Q$44,0))</f>
+      <c r="D13" s="19">
+        <f>INDEX(Raw_Data!$O$2:$O$44,MATCH(B13,Raw_Data!$Q$2:$Q$44,0))</f>
         <v>55829.3</v>
       </c>
-      <c r="F13" s="19"/>
-      <c r="G13" s="19"/>
-      <c r="H13" s="19"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="17" t="n">
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B14" s="18">
         <v>3</v>
       </c>
-      <c r="C14" s="17" t="str">
-        <f aca="false">INDEX(Raw_Data!$B$2:$B$44,MATCH(B14,Raw_Data!$Q$2:$Q$44,0))</f>
+      <c r="C14" s="18" t="str">
+        <f>INDEX(Raw_Data!$B$2:$B$44,MATCH(B14,Raw_Data!$Q$2:$Q$44,0))</f>
         <v>Tea Powder 250g</v>
       </c>
-      <c r="D14" s="18" t="n">
-        <f aca="false">INDEX(Raw_Data!$O$2:$O$44,MATCH(B14,Raw_Data!$Q$2:$Q$44,0))</f>
+      <c r="D14" s="19">
+        <f>INDEX(Raw_Data!$O$2:$O$44,MATCH(B14,Raw_Data!$Q$2:$Q$44,0))</f>
         <v>53844.21</v>
       </c>
-      <c r="F14" s="19"/>
-      <c r="G14" s="19"/>
-      <c r="H14" s="19"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="17" t="n">
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B15" s="18">
         <v>4</v>
       </c>
-      <c r="C15" s="17" t="str">
-        <f aca="false">INDEX(Raw_Data!$B$2:$B$44,MATCH(B15,Raw_Data!$Q$2:$Q$44,0))</f>
+      <c r="C15" s="18" t="str">
+        <f>INDEX(Raw_Data!$B$2:$B$44,MATCH(B15,Raw_Data!$Q$2:$Q$44,0))</f>
         <v>Energy Drink 250ml</v>
       </c>
-      <c r="D15" s="18" t="n">
-        <f aca="false">INDEX(Raw_Data!$O$2:$O$44,MATCH(B15,Raw_Data!$Q$2:$Q$44,0))</f>
-        <v>51074.24</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="17" t="n">
+      <c r="D15" s="19">
+        <f>INDEX(Raw_Data!$O$2:$O$44,MATCH(B15,Raw_Data!$Q$2:$Q$44,0))</f>
+        <v>51074.239999999998</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B16" s="18">
         <v>5</v>
       </c>
-      <c r="C16" s="17" t="str">
-        <f aca="false">INDEX(Raw_Data!$B$2:$B$44,MATCH(B16,Raw_Data!$Q$2:$Q$44,0))</f>
+      <c r="C16" s="18" t="str">
+        <f>INDEX(Raw_Data!$B$2:$B$44,MATCH(B16,Raw_Data!$Q$2:$Q$44,0))</f>
         <v>Floor Cleaner 1L</v>
       </c>
-      <c r="D16" s="18" t="n">
-        <f aca="false">INDEX(Raw_Data!$O$2:$O$44,MATCH(B16,Raw_Data!$Q$2:$Q$44,0))</f>
-        <v>49332.48</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="17" t="n">
+      <c r="D16" s="19">
+        <f>INDEX(Raw_Data!$O$2:$O$44,MATCH(B16,Raw_Data!$Q$2:$Q$44,0))</f>
+        <v>49332.479999999996</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B17" s="18">
         <v>6</v>
       </c>
-      <c r="C17" s="17" t="str">
-        <f aca="false">INDEX(Raw_Data!$B$2:$B$44,MATCH(B17,Raw_Data!$Q$2:$Q$44,0))</f>
+      <c r="C17" s="18" t="str">
+        <f>INDEX(Raw_Data!$B$2:$B$44,MATCH(B17,Raw_Data!$Q$2:$Q$44,0))</f>
         <v>Sev 200g</v>
       </c>
-      <c r="D17" s="18" t="n">
-        <f aca="false">INDEX(Raw_Data!$O$2:$O$44,MATCH(B17,Raw_Data!$Q$2:$Q$44,0))</f>
+      <c r="D17" s="19">
+        <f>INDEX(Raw_Data!$O$2:$O$44,MATCH(B17,Raw_Data!$Q$2:$Q$44,0))</f>
         <v>47573.75</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="17" t="n">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B18" s="18">
         <v>7</v>
       </c>
-      <c r="C18" s="17" t="str">
-        <f aca="false">INDEX(Raw_Data!$B$2:$B$44,MATCH(B18,Raw_Data!$Q$2:$Q$44,0))</f>
+      <c r="C18" s="18" t="str">
+        <f>INDEX(Raw_Data!$B$2:$B$44,MATCH(B18,Raw_Data!$Q$2:$Q$44,0))</f>
         <v>Razor Pack</v>
       </c>
-      <c r="D18" s="18" t="n">
-        <f aca="false">INDEX(Raw_Data!$O$2:$O$44,MATCH(B18,Raw_Data!$Q$2:$Q$44,0))</f>
+      <c r="D18" s="19">
+        <f>INDEX(Raw_Data!$O$2:$O$44,MATCH(B18,Raw_Data!$Q$2:$Q$44,0))</f>
         <v>46663.78</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="17" t="n">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B19" s="18">
         <v>8</v>
       </c>
-      <c r="C19" s="17" t="str">
-        <f aca="false">INDEX(Raw_Data!$B$2:$B$44,MATCH(B19,Raw_Data!$Q$2:$Q$44,0))</f>
+      <c r="C19" s="18" t="str">
+        <f>INDEX(Raw_Data!$B$2:$B$44,MATCH(B19,Raw_Data!$Q$2:$Q$44,0))</f>
         <v>Potato Chips 100g</v>
       </c>
-      <c r="D19" s="18" t="n">
-        <f aca="false">INDEX(Raw_Data!$O$2:$O$44,MATCH(B19,Raw_Data!$Q$2:$Q$44,0))</f>
+      <c r="D19" s="19">
+        <f>INDEX(Raw_Data!$O$2:$O$44,MATCH(B19,Raw_Data!$Q$2:$Q$44,0))</f>
         <v>42666.78</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="17" t="n">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B20" s="18">
         <v>9</v>
       </c>
-      <c r="C20" s="17" t="str">
-        <f aca="false">INDEX(Raw_Data!$B$2:$B$44,MATCH(B20,Raw_Data!$Q$2:$Q$44,0))</f>
+      <c r="C20" s="18" t="str">
+        <f>INDEX(Raw_Data!$B$2:$B$44,MATCH(B20,Raw_Data!$Q$2:$Q$44,0))</f>
         <v>Detergent Powder 1kg</v>
       </c>
-      <c r="D20" s="18" t="n">
-        <f aca="false">INDEX(Raw_Data!$O$2:$O$44,MATCH(B20,Raw_Data!$Q$2:$Q$44,0))</f>
-        <v>36277.6</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="17" t="n">
+      <c r="D20" s="19">
+        <f>INDEX(Raw_Data!$O$2:$O$44,MATCH(B20,Raw_Data!$Q$2:$Q$44,0))</f>
+        <v>36277.600000000006</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B21" s="18">
         <v>10</v>
       </c>
-      <c r="C21" s="17" t="str">
-        <f aca="false">INDEX(Raw_Data!$B$2:$B$44,MATCH(B21,Raw_Data!$Q$2:$Q$44,0))</f>
+      <c r="C21" s="18" t="str">
+        <f>INDEX(Raw_Data!$B$2:$B$44,MATCH(B21,Raw_Data!$Q$2:$Q$44,0))</f>
         <v>Wheat Flour 5kg</v>
       </c>
-      <c r="D21" s="18" t="n">
-        <f aca="false">INDEX(Raw_Data!$O$2:$O$44,MATCH(B21,Raw_Data!$Q$2:$Q$44,0))</f>
+      <c r="D21" s="19">
+        <f>INDEX(Raw_Data!$O$2:$O$44,MATCH(B21,Raw_Data!$Q$2:$Q$44,0))</f>
         <v>34979.1</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B6:C7"/>
+    <mergeCell ref="D6:E7"/>
+    <mergeCell ref="F6:G7"/>
+    <mergeCell ref="H6:I7"/>
+    <mergeCell ref="F12:H14"/>
     <mergeCell ref="B2:I2"/>
     <mergeCell ref="B3:I3"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="D5:E5"/>
     <mergeCell ref="F5:G5"/>
     <mergeCell ref="H5:I5"/>
-    <mergeCell ref="B6:C7"/>
-    <mergeCell ref="D6:E7"/>
-    <mergeCell ref="F6:G7"/>
-    <mergeCell ref="H6:I7"/>
-    <mergeCell ref="F12:H14"/>
   </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:Q44"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="14" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="10"/>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="5" width="16" customWidth="1"/>
+    <col min="6" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="11" width="12" customWidth="1"/>
+    <col min="12" max="12" width="14" customWidth="1"/>
+    <col min="13" max="13" width="10" customWidth="1"/>
+    <col min="14" max="15" width="16" customWidth="1"/>
+    <col min="16" max="16" width="18" customWidth="1"/>
+    <col min="17" max="17" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:17" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="20" t="s">
         <v>35</v>
       </c>
@@ -2192,8 +2147,8 @@
         <v>48</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="21" t="n">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A2" s="21">
         <v>1</v>
       </c>
       <c r="B2" s="21" t="s">
@@ -2202,58 +2157,58 @@
       <c r="C2" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="D2" s="22" t="n">
+      <c r="D2" s="22">
         <v>229.21</v>
       </c>
-      <c r="E2" s="22" t="n">
+      <c r="E2" s="22">
         <v>264.74</v>
       </c>
-      <c r="F2" s="21" t="n">
+      <c r="F2" s="21">
         <v>55</v>
       </c>
-      <c r="G2" s="21" t="n">
+      <c r="G2" s="21">
         <v>61</v>
       </c>
-      <c r="H2" s="21" t="n">
+      <c r="H2" s="21">
         <v>64</v>
       </c>
-      <c r="I2" s="21" t="n">
+      <c r="I2" s="21">
         <v>11</v>
       </c>
-      <c r="J2" s="17" t="n">
-        <f aca="false">F2+G2-H2-I2</f>
+      <c r="J2" s="18">
+        <f t="shared" ref="J2:J44" si="0">F2+G2-H2-I2</f>
         <v>41</v>
       </c>
-      <c r="K2" s="21" t="n">
+      <c r="K2" s="21">
         <v>36</v>
       </c>
       <c r="L2" s="23" t="str">
-        <f aca="false">IF(J2&lt;K2,"Reorder Now","OK")</f>
+        <f t="shared" ref="L2:L44" si="1">IF(J2&lt;K2,"Reorder Now","OK")</f>
         <v>OK</v>
       </c>
-      <c r="M2" s="24" t="n">
-        <f aca="false">IFERROR(I2/(H2+I2),0)</f>
-        <v>0.146666666666667</v>
-      </c>
-      <c r="N2" s="25" t="n">
-        <f aca="false">E2-D2</f>
+      <c r="M2" s="24">
+        <f t="shared" ref="M2:M44" si="2">IFERROR(I2/(H2+I2),0)</f>
+        <v>0.14666666666666667</v>
+      </c>
+      <c r="N2" s="25">
+        <f t="shared" ref="N2:N44" si="3">E2-D2</f>
         <v>35.53</v>
       </c>
-      <c r="O2" s="25" t="n">
-        <f aca="false">H2*E2</f>
+      <c r="O2" s="25">
+        <f t="shared" ref="O2:O44" si="4">H2*E2</f>
         <v>16943.36</v>
       </c>
-      <c r="P2" s="25" t="n">
-        <f aca="false">I2*D2</f>
+      <c r="P2" s="25">
+        <f t="shared" ref="P2:P44" si="5">I2*D2</f>
         <v>2521.31</v>
       </c>
-      <c r="Q2" s="17" t="n">
-        <f aca="false">RANK(O2,$O$2:$O$44,0)</f>
+      <c r="Q2" s="18">
+        <f t="shared" ref="Q2:Q44" si="6">RANK(O2,$O$2:$O$44,0)</f>
         <v>27</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="21" t="n">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A3" s="21">
         <v>2</v>
       </c>
       <c r="B3" s="21" t="s">
@@ -2262,58 +2217,58 @@
       <c r="C3" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="D3" s="22" t="n">
+      <c r="D3" s="22">
         <v>263.12</v>
       </c>
-      <c r="E3" s="22" t="n">
+      <c r="E3" s="22">
         <v>331.29</v>
       </c>
-      <c r="F3" s="21" t="n">
+      <c r="F3" s="21">
         <v>95</v>
       </c>
-      <c r="G3" s="21" t="n">
+      <c r="G3" s="21">
         <v>84</v>
       </c>
-      <c r="H3" s="21" t="n">
+      <c r="H3" s="21">
         <v>100</v>
       </c>
-      <c r="I3" s="21" t="n">
+      <c r="I3" s="21">
         <v>14</v>
       </c>
-      <c r="J3" s="17" t="n">
-        <f aca="false">F3+G3-H3-I3</f>
+      <c r="J3" s="18">
+        <f t="shared" si="0"/>
         <v>65</v>
       </c>
-      <c r="K3" s="21" t="n">
+      <c r="K3" s="21">
         <v>21</v>
       </c>
       <c r="L3" s="23" t="str">
-        <f aca="false">IF(J3&lt;K3,"Reorder Now","OK")</f>
+        <f t="shared" si="1"/>
         <v>OK</v>
       </c>
-      <c r="M3" s="24" t="n">
-        <f aca="false">IFERROR(I3/(H3+I3),0)</f>
-        <v>0.12280701754386</v>
-      </c>
-      <c r="N3" s="25" t="n">
-        <f aca="false">E3-D3</f>
-        <v>68.17</v>
-      </c>
-      <c r="O3" s="25" t="n">
-        <f aca="false">H3*E3</f>
+      <c r="M3" s="24">
+        <f t="shared" si="2"/>
+        <v>0.12280701754385964</v>
+      </c>
+      <c r="N3" s="25">
+        <f t="shared" si="3"/>
+        <v>68.170000000000016</v>
+      </c>
+      <c r="O3" s="25">
+        <f t="shared" si="4"/>
         <v>33129</v>
       </c>
-      <c r="P3" s="25" t="n">
-        <f aca="false">I3*D3</f>
-        <v>3683.68</v>
-      </c>
-      <c r="Q3" s="17" t="n">
-        <f aca="false">RANK(O3,$O$2:$O$44,0)</f>
+      <c r="P3" s="25">
+        <f t="shared" si="5"/>
+        <v>3683.6800000000003</v>
+      </c>
+      <c r="Q3" s="18">
+        <f t="shared" si="6"/>
         <v>13</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="21" t="n">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A4" s="21">
         <v>3</v>
       </c>
       <c r="B4" s="21" t="s">
@@ -2322,58 +2277,58 @@
       <c r="C4" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="D4" s="22" t="n">
+      <c r="D4" s="22">
         <v>92.94</v>
       </c>
-      <c r="E4" s="22" t="n">
+      <c r="E4" s="22">
         <v>118.07</v>
       </c>
-      <c r="F4" s="21" t="n">
+      <c r="F4" s="21">
         <v>91</v>
       </c>
-      <c r="G4" s="21" t="n">
+      <c r="G4" s="21">
         <v>55</v>
       </c>
-      <c r="H4" s="21" t="n">
+      <c r="H4" s="21">
         <v>117</v>
       </c>
-      <c r="I4" s="21" t="n">
+      <c r="I4" s="21">
         <v>22</v>
       </c>
-      <c r="J4" s="17" t="n">
-        <f aca="false">F4+G4-H4-I4</f>
+      <c r="J4" s="18">
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="K4" s="21" t="n">
+      <c r="K4" s="21">
         <v>32</v>
       </c>
       <c r="L4" s="23" t="str">
-        <f aca="false">IF(J4&lt;K4,"Reorder Now","OK")</f>
+        <f t="shared" si="1"/>
         <v>Reorder Now</v>
       </c>
-      <c r="M4" s="24" t="n">
-        <f aca="false">IFERROR(I4/(H4+I4),0)</f>
-        <v>0.158273381294964</v>
-      </c>
-      <c r="N4" s="25" t="n">
-        <f aca="false">E4-D4</f>
-        <v>25.13</v>
-      </c>
-      <c r="O4" s="25" t="n">
-        <f aca="false">H4*E4</f>
-        <v>13814.19</v>
-      </c>
-      <c r="P4" s="25" t="n">
-        <f aca="false">I4*D4</f>
-        <v>2044.68</v>
-      </c>
-      <c r="Q4" s="17" t="n">
-        <f aca="false">RANK(O4,$O$2:$O$44,0)</f>
+      <c r="M4" s="24">
+        <f t="shared" si="2"/>
+        <v>0.15827338129496402</v>
+      </c>
+      <c r="N4" s="25">
+        <f t="shared" si="3"/>
+        <v>25.129999999999995</v>
+      </c>
+      <c r="O4" s="25">
+        <f t="shared" si="4"/>
+        <v>13814.189999999999</v>
+      </c>
+      <c r="P4" s="25">
+        <f t="shared" si="5"/>
+        <v>2044.6799999999998</v>
+      </c>
+      <c r="Q4" s="18">
+        <f t="shared" si="6"/>
         <v>29</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="21" t="n">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A5" s="21">
         <v>4</v>
       </c>
       <c r="B5" s="21" t="s">
@@ -2382,58 +2337,58 @@
       <c r="C5" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="D5" s="22" t="n">
+      <c r="D5" s="22">
         <v>155.54</v>
       </c>
-      <c r="E5" s="22" t="n">
+      <c r="E5" s="22">
         <v>192.84</v>
       </c>
-      <c r="F5" s="21" t="n">
+      <c r="F5" s="21">
         <v>55</v>
       </c>
-      <c r="G5" s="21" t="n">
+      <c r="G5" s="21">
         <v>133</v>
       </c>
-      <c r="H5" s="21" t="n">
+      <c r="H5" s="21">
         <v>142</v>
       </c>
-      <c r="I5" s="21" t="n">
+      <c r="I5" s="21">
         <v>31</v>
       </c>
-      <c r="J5" s="17" t="n">
-        <f aca="false">F5+G5-H5-I5</f>
+      <c r="J5" s="18">
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="K5" s="21" t="n">
+      <c r="K5" s="21">
         <v>40</v>
       </c>
       <c r="L5" s="23" t="str">
-        <f aca="false">IF(J5&lt;K5,"Reorder Now","OK")</f>
+        <f t="shared" si="1"/>
         <v>Reorder Now</v>
       </c>
-      <c r="M5" s="24" t="n">
-        <f aca="false">IFERROR(I5/(H5+I5),0)</f>
-        <v>0.179190751445087</v>
-      </c>
-      <c r="N5" s="25" t="n">
-        <f aca="false">E5-D5</f>
-        <v>37.3</v>
-      </c>
-      <c r="O5" s="25" t="n">
-        <f aca="false">H5*E5</f>
-        <v>27383.28</v>
-      </c>
-      <c r="P5" s="25" t="n">
-        <f aca="false">I5*D5</f>
+      <c r="M5" s="24">
+        <f t="shared" si="2"/>
+        <v>0.1791907514450867</v>
+      </c>
+      <c r="N5" s="25">
+        <f t="shared" si="3"/>
+        <v>37.300000000000011</v>
+      </c>
+      <c r="O5" s="25">
+        <f t="shared" si="4"/>
+        <v>27383.279999999999</v>
+      </c>
+      <c r="P5" s="25">
+        <f t="shared" si="5"/>
         <v>4821.74</v>
       </c>
-      <c r="Q5" s="17" t="n">
-        <f aca="false">RANK(O5,$O$2:$O$44,0)</f>
+      <c r="Q5" s="18">
+        <f t="shared" si="6"/>
         <v>18</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="21" t="n">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A6" s="21">
         <v>5</v>
       </c>
       <c r="B6" s="21" t="s">
@@ -2442,58 +2397,58 @@
       <c r="C6" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="D6" s="22" t="n">
-        <v>68.49</v>
-      </c>
-      <c r="E6" s="22" t="n">
+      <c r="D6" s="22">
+        <v>68.489999999999995</v>
+      </c>
+      <c r="E6" s="22">
         <v>84.55</v>
       </c>
-      <c r="F6" s="21" t="n">
+      <c r="F6" s="21">
         <v>55</v>
       </c>
-      <c r="G6" s="21" t="n">
+      <c r="G6" s="21">
         <v>49</v>
       </c>
-      <c r="H6" s="21" t="n">
+      <c r="H6" s="21">
         <v>73</v>
       </c>
-      <c r="I6" s="21" t="n">
+      <c r="I6" s="21">
         <v>10</v>
       </c>
-      <c r="J6" s="17" t="n">
-        <f aca="false">F6+G6-H6-I6</f>
+      <c r="J6" s="18">
+        <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="K6" s="21" t="n">
+      <c r="K6" s="21">
         <v>18</v>
       </c>
       <c r="L6" s="23" t="str">
-        <f aca="false">IF(J6&lt;K6,"Reorder Now","OK")</f>
+        <f t="shared" si="1"/>
         <v>OK</v>
       </c>
-      <c r="M6" s="24" t="n">
-        <f aca="false">IFERROR(I6/(H6+I6),0)</f>
-        <v>0.120481927710843</v>
-      </c>
-      <c r="N6" s="25" t="n">
-        <f aca="false">E6-D6</f>
-        <v>16.06</v>
-      </c>
-      <c r="O6" s="25" t="n">
-        <f aca="false">H6*E6</f>
+      <c r="M6" s="24">
+        <f t="shared" si="2"/>
+        <v>0.12048192771084337</v>
+      </c>
+      <c r="N6" s="25">
+        <f t="shared" si="3"/>
+        <v>16.060000000000002</v>
+      </c>
+      <c r="O6" s="25">
+        <f t="shared" si="4"/>
         <v>6172.15</v>
       </c>
-      <c r="P6" s="25" t="n">
-        <f aca="false">I6*D6</f>
+      <c r="P6" s="25">
+        <f t="shared" si="5"/>
         <v>684.9</v>
       </c>
-      <c r="Q6" s="17" t="n">
-        <f aca="false">RANK(O6,$O$2:$O$44,0)</f>
+      <c r="Q6" s="18">
+        <f t="shared" si="6"/>
         <v>38</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="21" t="n">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A7" s="21">
         <v>6</v>
       </c>
       <c r="B7" s="21" t="s">
@@ -2502,58 +2457,58 @@
       <c r="C7" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="D7" s="22" t="n">
+      <c r="D7" s="22">
         <v>46.07</v>
       </c>
-      <c r="E7" s="22" t="n">
+      <c r="E7" s="22">
         <v>53.87</v>
       </c>
-      <c r="F7" s="21" t="n">
+      <c r="F7" s="21">
         <v>64</v>
       </c>
-      <c r="G7" s="21" t="n">
+      <c r="G7" s="21">
         <v>107</v>
       </c>
-      <c r="H7" s="21" t="n">
+      <c r="H7" s="21">
         <v>90</v>
       </c>
-      <c r="I7" s="21" t="n">
+      <c r="I7" s="21">
         <v>18</v>
       </c>
-      <c r="J7" s="17" t="n">
-        <f aca="false">F7+G7-H7-I7</f>
+      <c r="J7" s="18">
+        <f t="shared" si="0"/>
         <v>63</v>
       </c>
-      <c r="K7" s="21" t="n">
+      <c r="K7" s="21">
         <v>38</v>
       </c>
       <c r="L7" s="23" t="str">
-        <f aca="false">IF(J7&lt;K7,"Reorder Now","OK")</f>
+        <f t="shared" si="1"/>
         <v>OK</v>
       </c>
-      <c r="M7" s="24" t="n">
-        <f aca="false">IFERROR(I7/(H7+I7),0)</f>
-        <v>0.166666666666667</v>
-      </c>
-      <c r="N7" s="25" t="n">
-        <f aca="false">E7-D7</f>
-        <v>7.8</v>
-      </c>
-      <c r="O7" s="25" t="n">
-        <f aca="false">H7*E7</f>
+      <c r="M7" s="24">
+        <f t="shared" si="2"/>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="N7" s="25">
+        <f t="shared" si="3"/>
+        <v>7.7999999999999972</v>
+      </c>
+      <c r="O7" s="25">
+        <f t="shared" si="4"/>
         <v>4848.3</v>
       </c>
-      <c r="P7" s="25" t="n">
-        <f aca="false">I7*D7</f>
+      <c r="P7" s="25">
+        <f t="shared" si="5"/>
         <v>829.26</v>
       </c>
-      <c r="Q7" s="17" t="n">
-        <f aca="false">RANK(O7,$O$2:$O$44,0)</f>
+      <c r="Q7" s="18">
+        <f t="shared" si="6"/>
         <v>39</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="21" t="n">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A8" s="21">
         <v>7</v>
       </c>
       <c r="B8" s="21" t="s">
@@ -2562,58 +2517,58 @@
       <c r="C8" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="D8" s="22" t="n">
+      <c r="D8" s="22">
         <v>168.91</v>
       </c>
-      <c r="E8" s="22" t="n">
+      <c r="E8" s="22">
         <v>198.46</v>
       </c>
-      <c r="F8" s="21" t="n">
+      <c r="F8" s="21">
         <v>68</v>
       </c>
-      <c r="G8" s="21" t="n">
+      <c r="G8" s="21">
         <v>40</v>
       </c>
-      <c r="H8" s="21" t="n">
+      <c r="H8" s="21">
         <v>77</v>
       </c>
-      <c r="I8" s="21" t="n">
+      <c r="I8" s="21">
         <v>14</v>
       </c>
-      <c r="J8" s="17" t="n">
-        <f aca="false">F8+G8-H8-I8</f>
+      <c r="J8" s="18">
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="K8" s="21" t="n">
+      <c r="K8" s="21">
         <v>33</v>
       </c>
       <c r="L8" s="23" t="str">
-        <f aca="false">IF(J8&lt;K8,"Reorder Now","OK")</f>
+        <f t="shared" si="1"/>
         <v>Reorder Now</v>
       </c>
-      <c r="M8" s="24" t="n">
-        <f aca="false">IFERROR(I8/(H8+I8),0)</f>
-        <v>0.153846153846154</v>
-      </c>
-      <c r="N8" s="25" t="n">
-        <f aca="false">E8-D8</f>
-        <v>29.55</v>
-      </c>
-      <c r="O8" s="25" t="n">
-        <f aca="false">H8*E8</f>
+      <c r="M8" s="24">
+        <f t="shared" si="2"/>
+        <v>0.15384615384615385</v>
+      </c>
+      <c r="N8" s="25">
+        <f t="shared" si="3"/>
+        <v>29.550000000000011</v>
+      </c>
+      <c r="O8" s="25">
+        <f t="shared" si="4"/>
         <v>15281.42</v>
       </c>
-      <c r="P8" s="25" t="n">
-        <f aca="false">I8*D8</f>
-        <v>2364.74</v>
-      </c>
-      <c r="Q8" s="17" t="n">
-        <f aca="false">RANK(O8,$O$2:$O$44,0)</f>
+      <c r="P8" s="25">
+        <f t="shared" si="5"/>
+        <v>2364.7399999999998</v>
+      </c>
+      <c r="Q8" s="18">
+        <f t="shared" si="6"/>
         <v>28</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="21" t="n">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A9" s="21">
         <v>8</v>
       </c>
       <c r="B9" s="21" t="s">
@@ -2622,58 +2577,58 @@
       <c r="C9" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="D9" s="22" t="n">
+      <c r="D9" s="22">
         <v>79.42</v>
       </c>
-      <c r="E9" s="22" t="n">
+      <c r="E9" s="22">
         <v>92.44</v>
       </c>
-      <c r="F9" s="21" t="n">
+      <c r="F9" s="21">
         <v>104</v>
       </c>
-      <c r="G9" s="21" t="n">
+      <c r="G9" s="21">
         <v>59</v>
       </c>
-      <c r="H9" s="21" t="n">
+      <c r="H9" s="21">
         <v>91</v>
       </c>
-      <c r="I9" s="21" t="n">
+      <c r="I9" s="21">
         <v>9</v>
       </c>
-      <c r="J9" s="17" t="n">
-        <f aca="false">F9+G9-H9-I9</f>
+      <c r="J9" s="18">
+        <f t="shared" si="0"/>
         <v>63</v>
       </c>
-      <c r="K9" s="21" t="n">
+      <c r="K9" s="21">
         <v>22</v>
       </c>
       <c r="L9" s="23" t="str">
-        <f aca="false">IF(J9&lt;K9,"Reorder Now","OK")</f>
+        <f t="shared" si="1"/>
         <v>OK</v>
       </c>
-      <c r="M9" s="24" t="n">
-        <f aca="false">IFERROR(I9/(H9+I9),0)</f>
+      <c r="M9" s="24">
+        <f t="shared" si="2"/>
         <v>0.09</v>
       </c>
-      <c r="N9" s="25" t="n">
-        <f aca="false">E9-D9</f>
-        <v>13.02</v>
-      </c>
-      <c r="O9" s="25" t="n">
-        <f aca="false">H9*E9</f>
-        <v>8412.04</v>
-      </c>
-      <c r="P9" s="25" t="n">
-        <f aca="false">I9*D9</f>
+      <c r="N9" s="25">
+        <f t="shared" si="3"/>
+        <v>13.019999999999996</v>
+      </c>
+      <c r="O9" s="25">
+        <f t="shared" si="4"/>
+        <v>8412.0399999999991</v>
+      </c>
+      <c r="P9" s="25">
+        <f t="shared" si="5"/>
         <v>714.78</v>
       </c>
-      <c r="Q9" s="17" t="n">
-        <f aca="false">RANK(O9,$O$2:$O$44,0)</f>
+      <c r="Q9" s="18">
+        <f t="shared" si="6"/>
         <v>36</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="21" t="n">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A10" s="21">
         <v>9</v>
       </c>
       <c r="B10" s="21" t="s">
@@ -2682,58 +2637,58 @@
       <c r="C10" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="D10" s="22" t="n">
+      <c r="D10" s="22">
         <v>305.27</v>
       </c>
-      <c r="E10" s="22" t="n">
+      <c r="E10" s="22">
         <v>374.27</v>
       </c>
-      <c r="F10" s="21" t="n">
+      <c r="F10" s="21">
         <v>78</v>
       </c>
-      <c r="G10" s="21" t="n">
+      <c r="G10" s="21">
         <v>111</v>
       </c>
-      <c r="H10" s="21" t="n">
+      <c r="H10" s="21">
         <v>114</v>
       </c>
-      <c r="I10" s="21" t="n">
+      <c r="I10" s="21">
         <v>11</v>
       </c>
-      <c r="J10" s="17" t="n">
-        <f aca="false">F10+G10-H10-I10</f>
+      <c r="J10" s="18">
+        <f t="shared" si="0"/>
         <v>64</v>
       </c>
-      <c r="K10" s="21" t="n">
+      <c r="K10" s="21">
         <v>26</v>
       </c>
       <c r="L10" s="23" t="str">
-        <f aca="false">IF(J10&lt;K10,"Reorder Now","OK")</f>
+        <f t="shared" si="1"/>
         <v>OK</v>
       </c>
-      <c r="M10" s="24" t="n">
-        <f aca="false">IFERROR(I10/(H10+I10),0)</f>
-        <v>0.088</v>
-      </c>
-      <c r="N10" s="25" t="n">
-        <f aca="false">E10-D10</f>
+      <c r="M10" s="24">
+        <f t="shared" si="2"/>
+        <v>8.7999999999999995E-2</v>
+      </c>
+      <c r="N10" s="25">
+        <f t="shared" si="3"/>
         <v>69</v>
       </c>
-      <c r="O10" s="25" t="n">
-        <f aca="false">H10*E10</f>
+      <c r="O10" s="25">
+        <f t="shared" si="4"/>
         <v>42666.78</v>
       </c>
-      <c r="P10" s="25" t="n">
-        <f aca="false">I10*D10</f>
+      <c r="P10" s="25">
+        <f t="shared" si="5"/>
         <v>3357.97</v>
       </c>
-      <c r="Q10" s="17" t="n">
-        <f aca="false">RANK(O10,$O$2:$O$44,0)</f>
+      <c r="Q10" s="18">
+        <f t="shared" si="6"/>
         <v>8</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="21" t="n">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A11" s="21">
         <v>10</v>
       </c>
       <c r="B11" s="21" t="s">
@@ -2742,58 +2697,58 @@
       <c r="C11" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="D11" s="22" t="n">
-        <v>134.02</v>
-      </c>
-      <c r="E11" s="22" t="n">
+      <c r="D11" s="22">
+        <v>134.02000000000001</v>
+      </c>
+      <c r="E11" s="22">
         <v>172.09</v>
       </c>
-      <c r="F11" s="21" t="n">
+      <c r="F11" s="21">
         <v>109</v>
       </c>
-      <c r="G11" s="21" t="n">
+      <c r="G11" s="21">
         <v>149</v>
       </c>
-      <c r="H11" s="21" t="n">
+      <c r="H11" s="21">
         <v>138</v>
       </c>
-      <c r="I11" s="21" t="n">
+      <c r="I11" s="21">
         <v>13</v>
       </c>
-      <c r="J11" s="17" t="n">
-        <f aca="false">F11+G11-H11-I11</f>
+      <c r="J11" s="18">
+        <f t="shared" si="0"/>
         <v>107</v>
       </c>
-      <c r="K11" s="21" t="n">
+      <c r="K11" s="21">
         <v>34</v>
       </c>
       <c r="L11" s="23" t="str">
-        <f aca="false">IF(J11&lt;K11,"Reorder Now","OK")</f>
+        <f t="shared" si="1"/>
         <v>OK</v>
       </c>
-      <c r="M11" s="24" t="n">
-        <f aca="false">IFERROR(I11/(H11+I11),0)</f>
-        <v>0.0860927152317881</v>
-      </c>
-      <c r="N11" s="25" t="n">
-        <f aca="false">E11-D11</f>
-        <v>38.07</v>
-      </c>
-      <c r="O11" s="25" t="n">
-        <f aca="false">H11*E11</f>
-        <v>23748.42</v>
-      </c>
-      <c r="P11" s="25" t="n">
-        <f aca="false">I11*D11</f>
-        <v>1742.26</v>
-      </c>
-      <c r="Q11" s="17" t="n">
-        <f aca="false">RANK(O11,$O$2:$O$44,0)</f>
+      <c r="M11" s="24">
+        <f t="shared" si="2"/>
+        <v>8.6092715231788075E-2</v>
+      </c>
+      <c r="N11" s="25">
+        <f t="shared" si="3"/>
+        <v>38.069999999999993</v>
+      </c>
+      <c r="O11" s="25">
+        <f t="shared" si="4"/>
+        <v>23748.420000000002</v>
+      </c>
+      <c r="P11" s="25">
+        <f t="shared" si="5"/>
+        <v>1742.2600000000002</v>
+      </c>
+      <c r="Q11" s="18">
+        <f t="shared" si="6"/>
         <v>22</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="21" t="n">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A12" s="21">
         <v>11</v>
       </c>
       <c r="B12" s="21" t="s">
@@ -2802,58 +2757,58 @@
       <c r="C12" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="D12" s="22" t="n">
+      <c r="D12" s="22">
         <v>227.72</v>
       </c>
-      <c r="E12" s="22" t="n">
+      <c r="E12" s="22">
         <v>286.2</v>
       </c>
-      <c r="F12" s="21" t="n">
+      <c r="F12" s="21">
         <v>51</v>
       </c>
-      <c r="G12" s="21" t="n">
+      <c r="G12" s="21">
         <v>50</v>
       </c>
-      <c r="H12" s="21" t="n">
+      <c r="H12" s="21">
         <v>67</v>
       </c>
-      <c r="I12" s="21" t="n">
+      <c r="I12" s="21">
         <v>3</v>
       </c>
-      <c r="J12" s="17" t="n">
-        <f aca="false">F12+G12-H12-I12</f>
+      <c r="J12" s="18">
+        <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="K12" s="21" t="n">
+      <c r="K12" s="21">
         <v>35</v>
       </c>
       <c r="L12" s="23" t="str">
-        <f aca="false">IF(J12&lt;K12,"Reorder Now","OK")</f>
+        <f t="shared" si="1"/>
         <v>Reorder Now</v>
       </c>
-      <c r="M12" s="24" t="n">
-        <f aca="false">IFERROR(I12/(H12+I12),0)</f>
-        <v>0.0428571428571429</v>
-      </c>
-      <c r="N12" s="25" t="n">
-        <f aca="false">E12-D12</f>
-        <v>58.48</v>
-      </c>
-      <c r="O12" s="25" t="n">
-        <f aca="false">H12*E12</f>
-        <v>19175.4</v>
-      </c>
-      <c r="P12" s="25" t="n">
-        <f aca="false">I12*D12</f>
+      <c r="M12" s="24">
+        <f t="shared" si="2"/>
+        <v>4.2857142857142858E-2</v>
+      </c>
+      <c r="N12" s="25">
+        <f t="shared" si="3"/>
+        <v>58.47999999999999</v>
+      </c>
+      <c r="O12" s="25">
+        <f t="shared" si="4"/>
+        <v>19175.399999999998</v>
+      </c>
+      <c r="P12" s="25">
+        <f t="shared" si="5"/>
         <v>683.16</v>
       </c>
-      <c r="Q12" s="17" t="n">
-        <f aca="false">RANK(O12,$O$2:$O$44,0)</f>
+      <c r="Q12" s="18">
+        <f t="shared" si="6"/>
         <v>26</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="21" t="n">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A13" s="21">
         <v>12</v>
       </c>
       <c r="B13" s="21" t="s">
@@ -2862,58 +2817,58 @@
       <c r="C13" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="D13" s="22" t="n">
+      <c r="D13" s="22">
         <v>245.53</v>
       </c>
-      <c r="E13" s="22" t="n">
+      <c r="E13" s="22">
         <v>293.14</v>
       </c>
-      <c r="F13" s="21" t="n">
+      <c r="F13" s="21">
         <v>61</v>
       </c>
-      <c r="G13" s="21" t="n">
+      <c r="G13" s="21">
         <v>137</v>
       </c>
-      <c r="H13" s="21" t="n">
+      <c r="H13" s="21">
         <v>106</v>
       </c>
-      <c r="I13" s="21" t="n">
+      <c r="I13" s="21">
         <v>11</v>
       </c>
-      <c r="J13" s="17" t="n">
-        <f aca="false">F13+G13-H13-I13</f>
+      <c r="J13" s="18">
+        <f t="shared" si="0"/>
         <v>81</v>
       </c>
-      <c r="K13" s="21" t="n">
+      <c r="K13" s="21">
         <v>22</v>
       </c>
       <c r="L13" s="23" t="str">
-        <f aca="false">IF(J13&lt;K13,"Reorder Now","OK")</f>
+        <f t="shared" si="1"/>
         <v>OK</v>
       </c>
-      <c r="M13" s="24" t="n">
-        <f aca="false">IFERROR(I13/(H13+I13),0)</f>
-        <v>0.094017094017094</v>
-      </c>
-      <c r="N13" s="25" t="n">
-        <f aca="false">E13-D13</f>
-        <v>47.61</v>
-      </c>
-      <c r="O13" s="25" t="n">
-        <f aca="false">H13*E13</f>
+      <c r="M13" s="24">
+        <f t="shared" si="2"/>
+        <v>9.4017094017094016E-2</v>
+      </c>
+      <c r="N13" s="25">
+        <f t="shared" si="3"/>
+        <v>47.609999999999985</v>
+      </c>
+      <c r="O13" s="25">
+        <f t="shared" si="4"/>
         <v>31072.84</v>
       </c>
-      <c r="P13" s="25" t="n">
-        <f aca="false">I13*D13</f>
+      <c r="P13" s="25">
+        <f t="shared" si="5"/>
         <v>2700.83</v>
       </c>
-      <c r="Q13" s="17" t="n">
-        <f aca="false">RANK(O13,$O$2:$O$44,0)</f>
+      <c r="Q13" s="18">
+        <f t="shared" si="6"/>
         <v>14</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="21" t="n">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A14" s="21">
         <v>13</v>
       </c>
       <c r="B14" s="21" t="s">
@@ -2922,58 +2877,58 @@
       <c r="C14" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="D14" s="22" t="n">
+      <c r="D14" s="22">
         <v>290.3</v>
       </c>
-      <c r="E14" s="22" t="n">
+      <c r="E14" s="22">
         <v>380.59</v>
       </c>
-      <c r="F14" s="21" t="n">
+      <c r="F14" s="21">
         <v>71</v>
       </c>
-      <c r="G14" s="21" t="n">
+      <c r="G14" s="21">
         <v>64</v>
       </c>
-      <c r="H14" s="21" t="n">
+      <c r="H14" s="21">
         <v>125</v>
       </c>
-      <c r="I14" s="21" t="n">
+      <c r="I14" s="21">
         <v>1</v>
       </c>
-      <c r="J14" s="17" t="n">
-        <f aca="false">F14+G14-H14-I14</f>
+      <c r="J14" s="18">
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="K14" s="21" t="n">
+      <c r="K14" s="21">
         <v>33</v>
       </c>
       <c r="L14" s="23" t="str">
-        <f aca="false">IF(J14&lt;K14,"Reorder Now","OK")</f>
+        <f t="shared" si="1"/>
         <v>Reorder Now</v>
       </c>
-      <c r="M14" s="24" t="n">
-        <f aca="false">IFERROR(I14/(H14+I14),0)</f>
-        <v>0.00793650793650794</v>
-      </c>
-      <c r="N14" s="25" t="n">
-        <f aca="false">E14-D14</f>
-        <v>90.29</v>
-      </c>
-      <c r="O14" s="25" t="n">
-        <f aca="false">H14*E14</f>
+      <c r="M14" s="24">
+        <f t="shared" si="2"/>
+        <v>7.9365079365079361E-3</v>
+      </c>
+      <c r="N14" s="25">
+        <f t="shared" si="3"/>
+        <v>90.289999999999964</v>
+      </c>
+      <c r="O14" s="25">
+        <f t="shared" si="4"/>
         <v>47573.75</v>
       </c>
-      <c r="P14" s="25" t="n">
-        <f aca="false">I14*D14</f>
+      <c r="P14" s="25">
+        <f t="shared" si="5"/>
         <v>290.3</v>
       </c>
-      <c r="Q14" s="17" t="n">
-        <f aca="false">RANK(O14,$O$2:$O$44,0)</f>
+      <c r="Q14" s="18">
+        <f t="shared" si="6"/>
         <v>6</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="21" t="n">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A15" s="21">
         <v>14</v>
       </c>
       <c r="B15" s="21" t="s">
@@ -2982,58 +2937,58 @@
       <c r="C15" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="D15" s="22" t="n">
+      <c r="D15" s="22">
         <v>308.58</v>
       </c>
-      <c r="E15" s="22" t="n">
+      <c r="E15" s="22">
         <v>374.29</v>
       </c>
-      <c r="F15" s="21" t="n">
+      <c r="F15" s="21">
         <v>103</v>
       </c>
-      <c r="G15" s="21" t="n">
+      <c r="G15" s="21">
         <v>93</v>
       </c>
-      <c r="H15" s="21" t="n">
+      <c r="H15" s="21">
         <v>180</v>
       </c>
-      <c r="I15" s="21" t="n">
+      <c r="I15" s="21">
         <v>6</v>
       </c>
-      <c r="J15" s="17" t="n">
-        <f aca="false">F15+G15-H15-I15</f>
+      <c r="J15" s="18">
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="K15" s="21" t="n">
+      <c r="K15" s="21">
         <v>29</v>
       </c>
       <c r="L15" s="23" t="str">
-        <f aca="false">IF(J15&lt;K15,"Reorder Now","OK")</f>
+        <f t="shared" si="1"/>
         <v>Reorder Now</v>
       </c>
-      <c r="M15" s="24" t="n">
-        <f aca="false">IFERROR(I15/(H15+I15),0)</f>
-        <v>0.032258064516129</v>
-      </c>
-      <c r="N15" s="25" t="n">
-        <f aca="false">E15-D15</f>
-        <v>65.71</v>
-      </c>
-      <c r="O15" s="25" t="n">
-        <f aca="false">H15*E15</f>
+      <c r="M15" s="24">
+        <f t="shared" si="2"/>
+        <v>3.2258064516129031E-2</v>
+      </c>
+      <c r="N15" s="25">
+        <f t="shared" si="3"/>
+        <v>65.710000000000036</v>
+      </c>
+      <c r="O15" s="25">
+        <f t="shared" si="4"/>
         <v>67372.2</v>
       </c>
-      <c r="P15" s="25" t="n">
-        <f aca="false">I15*D15</f>
+      <c r="P15" s="25">
+        <f t="shared" si="5"/>
         <v>1851.48</v>
       </c>
-      <c r="Q15" s="17" t="n">
-        <f aca="false">RANK(O15,$O$2:$O$44,0)</f>
+      <c r="Q15" s="18">
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="21" t="n">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A16" s="21">
         <v>15</v>
       </c>
       <c r="B16" s="21" t="s">
@@ -3042,58 +2997,58 @@
       <c r="C16" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="D16" s="22" t="n">
+      <c r="D16" s="22">
         <v>62.86</v>
       </c>
-      <c r="E16" s="22" t="n">
-        <v>74.04</v>
-      </c>
-      <c r="F16" s="21" t="n">
+      <c r="E16" s="22">
+        <v>74.040000000000006</v>
+      </c>
+      <c r="F16" s="21">
         <v>115</v>
       </c>
-      <c r="G16" s="21" t="n">
+      <c r="G16" s="21">
         <v>101</v>
       </c>
-      <c r="H16" s="21" t="n">
+      <c r="H16" s="21">
         <v>182</v>
       </c>
-      <c r="I16" s="21" t="n">
+      <c r="I16" s="21">
         <v>9</v>
       </c>
-      <c r="J16" s="17" t="n">
-        <f aca="false">F16+G16-H16-I16</f>
+      <c r="J16" s="18">
+        <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="K16" s="21" t="n">
+      <c r="K16" s="21">
         <v>28</v>
       </c>
       <c r="L16" s="23" t="str">
-        <f aca="false">IF(J16&lt;K16,"Reorder Now","OK")</f>
+        <f t="shared" si="1"/>
         <v>Reorder Now</v>
       </c>
-      <c r="M16" s="24" t="n">
-        <f aca="false">IFERROR(I16/(H16+I16),0)</f>
-        <v>0.0471204188481675</v>
-      </c>
-      <c r="N16" s="25" t="n">
-        <f aca="false">E16-D16</f>
-        <v>11.18</v>
-      </c>
-      <c r="O16" s="25" t="n">
-        <f aca="false">H16*E16</f>
+      <c r="M16" s="24">
+        <f t="shared" si="2"/>
+        <v>4.712041884816754E-2</v>
+      </c>
+      <c r="N16" s="25">
+        <f t="shared" si="3"/>
+        <v>11.180000000000007</v>
+      </c>
+      <c r="O16" s="25">
+        <f t="shared" si="4"/>
         <v>13475.28</v>
       </c>
-      <c r="P16" s="25" t="n">
-        <f aca="false">I16*D16</f>
+      <c r="P16" s="25">
+        <f t="shared" si="5"/>
         <v>565.74</v>
       </c>
-      <c r="Q16" s="17" t="n">
-        <f aca="false">RANK(O16,$O$2:$O$44,0)</f>
+      <c r="Q16" s="18">
+        <f t="shared" si="6"/>
         <v>31</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="21" t="n">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A17" s="21">
         <v>16</v>
       </c>
       <c r="B17" s="21" t="s">
@@ -3102,58 +3057,58 @@
       <c r="C17" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="D17" s="22" t="n">
+      <c r="D17" s="22">
         <v>315.77</v>
       </c>
-      <c r="E17" s="22" t="n">
+      <c r="E17" s="22">
         <v>388.36</v>
       </c>
-      <c r="F17" s="21" t="n">
+      <c r="F17" s="21">
         <v>48</v>
       </c>
-      <c r="G17" s="21" t="n">
+      <c r="G17" s="21">
         <v>47</v>
       </c>
-      <c r="H17" s="21" t="n">
+      <c r="H17" s="21">
         <v>52</v>
       </c>
-      <c r="I17" s="21" t="n">
+      <c r="I17" s="21">
         <v>3</v>
       </c>
-      <c r="J17" s="17" t="n">
-        <f aca="false">F17+G17-H17-I17</f>
+      <c r="J17" s="18">
+        <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="K17" s="21" t="n">
+      <c r="K17" s="21">
         <v>39</v>
       </c>
       <c r="L17" s="23" t="str">
-        <f aca="false">IF(J17&lt;K17,"Reorder Now","OK")</f>
+        <f t="shared" si="1"/>
         <v>OK</v>
       </c>
-      <c r="M17" s="24" t="n">
-        <f aca="false">IFERROR(I17/(H17+I17),0)</f>
-        <v>0.0545454545454545</v>
-      </c>
-      <c r="N17" s="25" t="n">
-        <f aca="false">E17-D17</f>
-        <v>72.59</v>
-      </c>
-      <c r="O17" s="25" t="n">
-        <f aca="false">H17*E17</f>
+      <c r="M17" s="24">
+        <f t="shared" si="2"/>
+        <v>5.4545454545454543E-2</v>
+      </c>
+      <c r="N17" s="25">
+        <f t="shared" si="3"/>
+        <v>72.590000000000032</v>
+      </c>
+      <c r="O17" s="25">
+        <f t="shared" si="4"/>
         <v>20194.72</v>
       </c>
-      <c r="P17" s="25" t="n">
-        <f aca="false">I17*D17</f>
+      <c r="P17" s="25">
+        <f t="shared" si="5"/>
         <v>947.31</v>
       </c>
-      <c r="Q17" s="17" t="n">
-        <f aca="false">RANK(O17,$O$2:$O$44,0)</f>
+      <c r="Q17" s="18">
+        <f t="shared" si="6"/>
         <v>25</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="21" t="n">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A18" s="21">
         <v>17</v>
       </c>
       <c r="B18" s="21" t="s">
@@ -3162,58 +3117,58 @@
       <c r="C18" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="D18" s="22" t="n">
+      <c r="D18" s="22">
         <v>30.78</v>
       </c>
-      <c r="E18" s="22" t="n">
+      <c r="E18" s="22">
         <v>36.07</v>
       </c>
-      <c r="F18" s="21" t="n">
+      <c r="F18" s="21">
         <v>100</v>
       </c>
-      <c r="G18" s="21" t="n">
+      <c r="G18" s="21">
         <v>50</v>
       </c>
-      <c r="H18" s="21" t="n">
+      <c r="H18" s="21">
         <v>102</v>
       </c>
-      <c r="I18" s="21" t="n">
+      <c r="I18" s="21">
         <v>8</v>
       </c>
-      <c r="J18" s="17" t="n">
-        <f aca="false">F18+G18-H18-I18</f>
+      <c r="J18" s="18">
+        <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="K18" s="21" t="n">
+      <c r="K18" s="21">
         <v>34</v>
       </c>
       <c r="L18" s="23" t="str">
-        <f aca="false">IF(J18&lt;K18,"Reorder Now","OK")</f>
+        <f t="shared" si="1"/>
         <v>OK</v>
       </c>
-      <c r="M18" s="24" t="n">
-        <f aca="false">IFERROR(I18/(H18+I18),0)</f>
-        <v>0.0727272727272727</v>
-      </c>
-      <c r="N18" s="25" t="n">
-        <f aca="false">E18-D18</f>
-        <v>5.29</v>
-      </c>
-      <c r="O18" s="25" t="n">
-        <f aca="false">H18*E18</f>
+      <c r="M18" s="24">
+        <f t="shared" si="2"/>
+        <v>7.2727272727272724E-2</v>
+      </c>
+      <c r="N18" s="25">
+        <f t="shared" si="3"/>
+        <v>5.2899999999999991</v>
+      </c>
+      <c r="O18" s="25">
+        <f t="shared" si="4"/>
         <v>3679.14</v>
       </c>
-      <c r="P18" s="25" t="n">
-        <f aca="false">I18*D18</f>
+      <c r="P18" s="25">
+        <f t="shared" si="5"/>
         <v>246.24</v>
       </c>
-      <c r="Q18" s="17" t="n">
-        <f aca="false">RANK(O18,$O$2:$O$44,0)</f>
+      <c r="Q18" s="18">
+        <f t="shared" si="6"/>
         <v>42</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="21" t="n">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A19" s="21">
         <v>18</v>
       </c>
       <c r="B19" s="21" t="s">
@@ -3222,58 +3177,58 @@
       <c r="C19" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="D19" s="22" t="n">
+      <c r="D19" s="22">
         <v>36.28</v>
       </c>
-      <c r="E19" s="22" t="n">
+      <c r="E19" s="22">
         <v>44.49</v>
       </c>
-      <c r="F19" s="21" t="n">
+      <c r="F19" s="21">
         <v>79</v>
       </c>
-      <c r="G19" s="21" t="n">
+      <c r="G19" s="21">
         <v>97</v>
       </c>
-      <c r="H19" s="21" t="n">
+      <c r="H19" s="21">
         <v>158</v>
       </c>
-      <c r="I19" s="21" t="n">
+      <c r="I19" s="21">
         <v>4</v>
       </c>
-      <c r="J19" s="17" t="n">
-        <f aca="false">F19+G19-H19-I19</f>
+      <c r="J19" s="18">
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="K19" s="21" t="n">
+      <c r="K19" s="21">
         <v>15</v>
       </c>
       <c r="L19" s="23" t="str">
-        <f aca="false">IF(J19&lt;K19,"Reorder Now","OK")</f>
+        <f t="shared" si="1"/>
         <v>Reorder Now</v>
       </c>
-      <c r="M19" s="24" t="n">
-        <f aca="false">IFERROR(I19/(H19+I19),0)</f>
-        <v>0.0246913580246914</v>
-      </c>
-      <c r="N19" s="25" t="n">
-        <f aca="false">E19-D19</f>
-        <v>8.21</v>
-      </c>
-      <c r="O19" s="25" t="n">
-        <f aca="false">H19*E19</f>
+      <c r="M19" s="24">
+        <f t="shared" si="2"/>
+        <v>2.4691358024691357E-2</v>
+      </c>
+      <c r="N19" s="25">
+        <f t="shared" si="3"/>
+        <v>8.2100000000000009</v>
+      </c>
+      <c r="O19" s="25">
+        <f t="shared" si="4"/>
         <v>7029.42</v>
       </c>
-      <c r="P19" s="25" t="n">
-        <f aca="false">I19*D19</f>
+      <c r="P19" s="25">
+        <f t="shared" si="5"/>
         <v>145.12</v>
       </c>
-      <c r="Q19" s="17" t="n">
-        <f aca="false">RANK(O19,$O$2:$O$44,0)</f>
+      <c r="Q19" s="18">
+        <f t="shared" si="6"/>
         <v>37</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="21" t="n">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A20" s="21">
         <v>19</v>
       </c>
       <c r="B20" s="21" t="s">
@@ -3282,58 +3237,58 @@
       <c r="C20" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="D20" s="22" t="n">
+      <c r="D20" s="22">
         <v>242.89</v>
       </c>
-      <c r="E20" s="22" t="n">
+      <c r="E20" s="22">
         <v>284.89</v>
       </c>
-      <c r="F20" s="21" t="n">
+      <c r="F20" s="21">
         <v>88</v>
       </c>
-      <c r="G20" s="21" t="n">
+      <c r="G20" s="21">
         <v>126</v>
       </c>
-      <c r="H20" s="21" t="n">
+      <c r="H20" s="21">
         <v>189</v>
       </c>
-      <c r="I20" s="21" t="n">
+      <c r="I20" s="21">
         <v>5</v>
       </c>
-      <c r="J20" s="17" t="n">
-        <f aca="false">F20+G20-H20-I20</f>
+      <c r="J20" s="18">
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="K20" s="21" t="n">
+      <c r="K20" s="21">
         <v>25</v>
       </c>
       <c r="L20" s="23" t="str">
-        <f aca="false">IF(J20&lt;K20,"Reorder Now","OK")</f>
+        <f t="shared" si="1"/>
         <v>Reorder Now</v>
       </c>
-      <c r="M20" s="24" t="n">
-        <f aca="false">IFERROR(I20/(H20+I20),0)</f>
-        <v>0.0257731958762887</v>
-      </c>
-      <c r="N20" s="25" t="n">
-        <f aca="false">E20-D20</f>
+      <c r="M20" s="24">
+        <f t="shared" si="2"/>
+        <v>2.5773195876288658E-2</v>
+      </c>
+      <c r="N20" s="25">
+        <f t="shared" si="3"/>
         <v>42</v>
       </c>
-      <c r="O20" s="25" t="n">
-        <f aca="false">H20*E20</f>
+      <c r="O20" s="25">
+        <f t="shared" si="4"/>
         <v>53844.21</v>
       </c>
-      <c r="P20" s="25" t="n">
-        <f aca="false">I20*D20</f>
-        <v>1214.45</v>
-      </c>
-      <c r="Q20" s="17" t="n">
-        <f aca="false">RANK(O20,$O$2:$O$44,0)</f>
+      <c r="P20" s="25">
+        <f t="shared" si="5"/>
+        <v>1214.4499999999998</v>
+      </c>
+      <c r="Q20" s="18">
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="21" t="n">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A21" s="21">
         <v>20</v>
       </c>
       <c r="B21" s="21" t="s">
@@ -3342,58 +3297,58 @@
       <c r="C21" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="D21" s="22" t="n">
+      <c r="D21" s="22">
         <v>52.37</v>
       </c>
-      <c r="E21" s="22" t="n">
+      <c r="E21" s="22">
         <v>64.78</v>
       </c>
-      <c r="F21" s="21" t="n">
+      <c r="F21" s="21">
         <v>78</v>
       </c>
-      <c r="G21" s="21" t="n">
+      <c r="G21" s="21">
         <v>30</v>
       </c>
-      <c r="H21" s="21" t="n">
+      <c r="H21" s="21">
         <v>70</v>
       </c>
-      <c r="I21" s="21" t="n">
+      <c r="I21" s="21">
         <v>7</v>
       </c>
-      <c r="J21" s="17" t="n">
-        <f aca="false">F21+G21-H21-I21</f>
+      <c r="J21" s="18">
+        <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="K21" s="21" t="n">
+      <c r="K21" s="21">
         <v>31</v>
       </c>
       <c r="L21" s="23" t="str">
-        <f aca="false">IF(J21&lt;K21,"Reorder Now","OK")</f>
+        <f t="shared" si="1"/>
         <v>OK</v>
       </c>
-      <c r="M21" s="24" t="n">
-        <f aca="false">IFERROR(I21/(H21+I21),0)</f>
-        <v>0.0909090909090909</v>
-      </c>
-      <c r="N21" s="25" t="n">
-        <f aca="false">E21-D21</f>
-        <v>12.41</v>
-      </c>
-      <c r="O21" s="25" t="n">
-        <f aca="false">H21*E21</f>
-        <v>4534.6</v>
-      </c>
-      <c r="P21" s="25" t="n">
-        <f aca="false">I21*D21</f>
+      <c r="M21" s="24">
+        <f t="shared" si="2"/>
+        <v>9.0909090909090912E-2</v>
+      </c>
+      <c r="N21" s="25">
+        <f t="shared" si="3"/>
+        <v>12.410000000000004</v>
+      </c>
+      <c r="O21" s="25">
+        <f t="shared" si="4"/>
+        <v>4534.6000000000004</v>
+      </c>
+      <c r="P21" s="25">
+        <f t="shared" si="5"/>
         <v>366.59</v>
       </c>
-      <c r="Q21" s="17" t="n">
-        <f aca="false">RANK(O21,$O$2:$O$44,0)</f>
+      <c r="Q21" s="18">
+        <f t="shared" si="6"/>
         <v>40</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="21" t="n">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A22" s="21">
         <v>21</v>
       </c>
       <c r="B22" s="21" t="s">
@@ -3402,58 +3357,58 @@
       <c r="C22" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="D22" s="22" t="n">
+      <c r="D22" s="22">
         <v>270.26</v>
       </c>
-      <c r="E22" s="22" t="n">
+      <c r="E22" s="22">
         <v>338.24</v>
       </c>
-      <c r="F22" s="21" t="n">
+      <c r="F22" s="21">
         <v>33</v>
       </c>
-      <c r="G22" s="21" t="n">
+      <c r="G22" s="21">
         <v>141</v>
       </c>
-      <c r="H22" s="21" t="n">
+      <c r="H22" s="21">
         <v>151</v>
       </c>
-      <c r="I22" s="21" t="n">
+      <c r="I22" s="21">
         <v>8</v>
       </c>
-      <c r="J22" s="17" t="n">
-        <f aca="false">F22+G22-H22-I22</f>
+      <c r="J22" s="18">
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="K22" s="21" t="n">
+      <c r="K22" s="21">
         <v>34</v>
       </c>
       <c r="L22" s="23" t="str">
-        <f aca="false">IF(J22&lt;K22,"Reorder Now","OK")</f>
+        <f t="shared" si="1"/>
         <v>Reorder Now</v>
       </c>
-      <c r="M22" s="24" t="n">
-        <f aca="false">IFERROR(I22/(H22+I22),0)</f>
-        <v>0.050314465408805</v>
-      </c>
-      <c r="N22" s="25" t="n">
-        <f aca="false">E22-D22</f>
-        <v>67.98</v>
-      </c>
-      <c r="O22" s="25" t="n">
-        <f aca="false">H22*E22</f>
-        <v>51074.24</v>
-      </c>
-      <c r="P22" s="25" t="n">
-        <f aca="false">I22*D22</f>
+      <c r="M22" s="24">
+        <f t="shared" si="2"/>
+        <v>5.0314465408805034E-2</v>
+      </c>
+      <c r="N22" s="25">
+        <f t="shared" si="3"/>
+        <v>67.980000000000018</v>
+      </c>
+      <c r="O22" s="25">
+        <f t="shared" si="4"/>
+        <v>51074.239999999998</v>
+      </c>
+      <c r="P22" s="25">
+        <f t="shared" si="5"/>
         <v>2162.08</v>
       </c>
-      <c r="Q22" s="17" t="n">
-        <f aca="false">RANK(O22,$O$2:$O$44,0)</f>
+      <c r="Q22" s="18">
+        <f t="shared" si="6"/>
         <v>4</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="21" t="n">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A23" s="21">
         <v>22</v>
       </c>
       <c r="B23" s="21" t="s">
@@ -3462,58 +3417,58 @@
       <c r="C23" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="D23" s="22" t="n">
+      <c r="D23" s="22">
         <v>81.64</v>
       </c>
-      <c r="E23" s="22" t="n">
+      <c r="E23" s="22">
         <v>99.99</v>
       </c>
-      <c r="F23" s="21" t="n">
+      <c r="F23" s="21">
         <v>40</v>
       </c>
-      <c r="G23" s="21" t="n">
+      <c r="G23" s="21">
         <v>99</v>
       </c>
-      <c r="H23" s="21" t="n">
+      <c r="H23" s="21">
         <v>102</v>
       </c>
-      <c r="I23" s="21" t="n">
+      <c r="I23" s="21">
         <v>9</v>
       </c>
-      <c r="J23" s="17" t="n">
-        <f aca="false">F23+G23-H23-I23</f>
+      <c r="J23" s="18">
+        <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="K23" s="21" t="n">
+      <c r="K23" s="21">
         <v>15</v>
       </c>
       <c r="L23" s="23" t="str">
-        <f aca="false">IF(J23&lt;K23,"Reorder Now","OK")</f>
+        <f t="shared" si="1"/>
         <v>OK</v>
       </c>
-      <c r="M23" s="24" t="n">
-        <f aca="false">IFERROR(I23/(H23+I23),0)</f>
-        <v>0.0810810810810811</v>
-      </c>
-      <c r="N23" s="25" t="n">
-        <f aca="false">E23-D23</f>
-        <v>18.35</v>
-      </c>
-      <c r="O23" s="25" t="n">
-        <f aca="false">H23*E23</f>
+      <c r="M23" s="24">
+        <f t="shared" si="2"/>
+        <v>8.1081081081081086E-2</v>
+      </c>
+      <c r="N23" s="25">
+        <f t="shared" si="3"/>
+        <v>18.349999999999994</v>
+      </c>
+      <c r="O23" s="25">
+        <f t="shared" si="4"/>
         <v>10198.98</v>
       </c>
-      <c r="P23" s="25" t="n">
-        <f aca="false">I23*D23</f>
+      <c r="P23" s="25">
+        <f t="shared" si="5"/>
         <v>734.76</v>
       </c>
-      <c r="Q23" s="17" t="n">
-        <f aca="false">RANK(O23,$O$2:$O$44,0)</f>
+      <c r="Q23" s="18">
+        <f t="shared" si="6"/>
         <v>35</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="21" t="n">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A24" s="21">
         <v>23</v>
       </c>
       <c r="B24" s="21" t="s">
@@ -3522,58 +3477,58 @@
       <c r="C24" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="D24" s="22" t="n">
+      <c r="D24" s="22">
         <v>215.65</v>
       </c>
-      <c r="E24" s="22" t="n">
+      <c r="E24" s="22">
         <v>269.07</v>
       </c>
-      <c r="F24" s="21" t="n">
+      <c r="F24" s="21">
         <v>34</v>
       </c>
-      <c r="G24" s="21" t="n">
+      <c r="G24" s="21">
         <v>148</v>
       </c>
-      <c r="H24" s="21" t="n">
+      <c r="H24" s="21">
         <v>130</v>
       </c>
-      <c r="I24" s="21" t="n">
+      <c r="I24" s="21">
         <v>5</v>
       </c>
-      <c r="J24" s="17" t="n">
-        <f aca="false">F24+G24-H24-I24</f>
+      <c r="J24" s="18">
+        <f t="shared" si="0"/>
         <v>47</v>
       </c>
-      <c r="K24" s="21" t="n">
+      <c r="K24" s="21">
         <v>22</v>
       </c>
       <c r="L24" s="23" t="str">
-        <f aca="false">IF(J24&lt;K24,"Reorder Now","OK")</f>
+        <f t="shared" si="1"/>
         <v>OK</v>
       </c>
-      <c r="M24" s="24" t="n">
-        <f aca="false">IFERROR(I24/(H24+I24),0)</f>
-        <v>0.037037037037037</v>
-      </c>
-      <c r="N24" s="25" t="n">
-        <f aca="false">E24-D24</f>
-        <v>53.42</v>
-      </c>
-      <c r="O24" s="25" t="n">
-        <f aca="false">H24*E24</f>
+      <c r="M24" s="24">
+        <f t="shared" si="2"/>
+        <v>3.7037037037037035E-2</v>
+      </c>
+      <c r="N24" s="25">
+        <f t="shared" si="3"/>
+        <v>53.419999999999987</v>
+      </c>
+      <c r="O24" s="25">
+        <f t="shared" si="4"/>
         <v>34979.1</v>
       </c>
-      <c r="P24" s="25" t="n">
-        <f aca="false">I24*D24</f>
+      <c r="P24" s="25">
+        <f t="shared" si="5"/>
         <v>1078.25</v>
       </c>
-      <c r="Q24" s="17" t="n">
-        <f aca="false">RANK(O24,$O$2:$O$44,0)</f>
+      <c r="Q24" s="18">
+        <f t="shared" si="6"/>
         <v>10</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="21" t="n">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A25" s="21">
         <v>24</v>
       </c>
       <c r="B25" s="21" t="s">
@@ -3582,58 +3537,58 @@
       <c r="C25" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="D25" s="22" t="n">
+      <c r="D25" s="22">
         <v>34.4</v>
       </c>
-      <c r="E25" s="22" t="n">
+      <c r="E25" s="22">
         <v>45.6</v>
       </c>
-      <c r="F25" s="21" t="n">
+      <c r="F25" s="21">
         <v>30</v>
       </c>
-      <c r="G25" s="21" t="n">
+      <c r="G25" s="21">
         <v>40</v>
       </c>
-      <c r="H25" s="21" t="n">
+      <c r="H25" s="21">
         <v>61</v>
       </c>
-      <c r="I25" s="21" t="n">
+      <c r="I25" s="21">
         <v>3</v>
       </c>
-      <c r="J25" s="17" t="n">
-        <f aca="false">F25+G25-H25-I25</f>
+      <c r="J25" s="18">
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="K25" s="21" t="n">
+      <c r="K25" s="21">
         <v>17</v>
       </c>
       <c r="L25" s="23" t="str">
-        <f aca="false">IF(J25&lt;K25,"Reorder Now","OK")</f>
+        <f t="shared" si="1"/>
         <v>Reorder Now</v>
       </c>
-      <c r="M25" s="24" t="n">
-        <f aca="false">IFERROR(I25/(H25+I25),0)</f>
-        <v>0.046875</v>
-      </c>
-      <c r="N25" s="25" t="n">
-        <f aca="false">E25-D25</f>
-        <v>11.2</v>
-      </c>
-      <c r="O25" s="25" t="n">
-        <f aca="false">H25*E25</f>
+      <c r="M25" s="24">
+        <f t="shared" si="2"/>
+        <v>4.6875E-2</v>
+      </c>
+      <c r="N25" s="25">
+        <f t="shared" si="3"/>
+        <v>11.200000000000003</v>
+      </c>
+      <c r="O25" s="25">
+        <f t="shared" si="4"/>
         <v>2781.6</v>
       </c>
-      <c r="P25" s="25" t="n">
-        <f aca="false">I25*D25</f>
-        <v>103.2</v>
-      </c>
-      <c r="Q25" s="17" t="n">
-        <f aca="false">RANK(O25,$O$2:$O$44,0)</f>
+      <c r="P25" s="25">
+        <f t="shared" si="5"/>
+        <v>103.19999999999999</v>
+      </c>
+      <c r="Q25" s="18">
+        <f t="shared" si="6"/>
         <v>43</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="21" t="n">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A26" s="21">
         <v>25</v>
       </c>
       <c r="B26" s="21" t="s">
@@ -3642,58 +3597,58 @@
       <c r="C26" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="D26" s="22" t="n">
+      <c r="D26" s="22">
         <v>342.62</v>
       </c>
-      <c r="E26" s="22" t="n">
+      <c r="E26" s="22">
         <v>430.52</v>
       </c>
-      <c r="F26" s="21" t="n">
+      <c r="F26" s="21">
         <v>36</v>
       </c>
-      <c r="G26" s="21" t="n">
+      <c r="G26" s="21">
         <v>46</v>
       </c>
-      <c r="H26" s="21" t="n">
+      <c r="H26" s="21">
         <v>51</v>
       </c>
-      <c r="I26" s="21" t="n">
+      <c r="I26" s="21">
         <v>4</v>
       </c>
-      <c r="J26" s="17" t="n">
-        <f aca="false">F26+G26-H26-I26</f>
+      <c r="J26" s="18">
+        <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="K26" s="21" t="n">
+      <c r="K26" s="21">
         <v>23</v>
       </c>
       <c r="L26" s="23" t="str">
-        <f aca="false">IF(J26&lt;K26,"Reorder Now","OK")</f>
+        <f t="shared" si="1"/>
         <v>OK</v>
       </c>
-      <c r="M26" s="24" t="n">
-        <f aca="false">IFERROR(I26/(H26+I26),0)</f>
-        <v>0.0727272727272727</v>
-      </c>
-      <c r="N26" s="25" t="n">
-        <f aca="false">E26-D26</f>
-        <v>87.9</v>
-      </c>
-      <c r="O26" s="25" t="n">
-        <f aca="false">H26*E26</f>
+      <c r="M26" s="24">
+        <f t="shared" si="2"/>
+        <v>7.2727272727272724E-2</v>
+      </c>
+      <c r="N26" s="25">
+        <f t="shared" si="3"/>
+        <v>87.899999999999977</v>
+      </c>
+      <c r="O26" s="25">
+        <f t="shared" si="4"/>
         <v>21956.52</v>
       </c>
-      <c r="P26" s="25" t="n">
-        <f aca="false">I26*D26</f>
+      <c r="P26" s="25">
+        <f t="shared" si="5"/>
         <v>1370.48</v>
       </c>
-      <c r="Q26" s="17" t="n">
-        <f aca="false">RANK(O26,$O$2:$O$44,0)</f>
+      <c r="Q26" s="18">
+        <f t="shared" si="6"/>
         <v>24</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="21" t="n">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A27" s="21">
         <v>26</v>
       </c>
       <c r="B27" s="21" t="s">
@@ -3702,58 +3657,58 @@
       <c r="C27" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="D27" s="22" t="n">
+      <c r="D27" s="22">
         <v>191.77</v>
       </c>
-      <c r="E27" s="22" t="n">
+      <c r="E27" s="22">
         <v>243.8</v>
       </c>
-      <c r="F27" s="21" t="n">
+      <c r="F27" s="21">
         <v>47</v>
       </c>
-      <c r="G27" s="21" t="n">
+      <c r="G27" s="21">
         <v>148</v>
       </c>
-      <c r="H27" s="21" t="n">
+      <c r="H27" s="21">
         <v>122</v>
       </c>
-      <c r="I27" s="21" t="n">
+      <c r="I27" s="21">
         <v>8</v>
       </c>
-      <c r="J27" s="17" t="n">
-        <f aca="false">F27+G27-H27-I27</f>
+      <c r="J27" s="18">
+        <f t="shared" si="0"/>
         <v>65</v>
       </c>
-      <c r="K27" s="21" t="n">
+      <c r="K27" s="21">
         <v>37</v>
       </c>
       <c r="L27" s="23" t="str">
-        <f aca="false">IF(J27&lt;K27,"Reorder Now","OK")</f>
+        <f t="shared" si="1"/>
         <v>OK</v>
       </c>
-      <c r="M27" s="24" t="n">
-        <f aca="false">IFERROR(I27/(H27+I27),0)</f>
-        <v>0.0615384615384615</v>
-      </c>
-      <c r="N27" s="25" t="n">
-        <f aca="false">E27-D27</f>
+      <c r="M27" s="24">
+        <f t="shared" si="2"/>
+        <v>6.1538461538461542E-2</v>
+      </c>
+      <c r="N27" s="25">
+        <f t="shared" si="3"/>
         <v>52.03</v>
       </c>
-      <c r="O27" s="25" t="n">
-        <f aca="false">H27*E27</f>
-        <v>29743.6</v>
-      </c>
-      <c r="P27" s="25" t="n">
-        <f aca="false">I27*D27</f>
+      <c r="O27" s="25">
+        <f t="shared" si="4"/>
+        <v>29743.600000000002</v>
+      </c>
+      <c r="P27" s="25">
+        <f t="shared" si="5"/>
         <v>1534.16</v>
       </c>
-      <c r="Q27" s="17" t="n">
-        <f aca="false">RANK(O27,$O$2:$O$44,0)</f>
+      <c r="Q27" s="18">
+        <f t="shared" si="6"/>
         <v>15</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="21" t="n">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A28" s="21">
         <v>27</v>
       </c>
       <c r="B28" s="21" t="s">
@@ -3762,58 +3717,58 @@
       <c r="C28" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="D28" s="22" t="n">
+      <c r="D28" s="22">
         <v>119.42</v>
       </c>
-      <c r="E28" s="22" t="n">
+      <c r="E28" s="22">
         <v>161.1</v>
       </c>
-      <c r="F28" s="21" t="n">
+      <c r="F28" s="21">
         <v>103</v>
       </c>
-      <c r="G28" s="21" t="n">
+      <c r="G28" s="21">
         <v>77</v>
       </c>
-      <c r="H28" s="21" t="n">
+      <c r="H28" s="21">
         <v>156</v>
       </c>
-      <c r="I28" s="21" t="n">
+      <c r="I28" s="21">
         <v>6</v>
       </c>
-      <c r="J28" s="17" t="n">
-        <f aca="false">F28+G28-H28-I28</f>
+      <c r="J28" s="18">
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="K28" s="21" t="n">
+      <c r="K28" s="21">
         <v>29</v>
       </c>
       <c r="L28" s="23" t="str">
-        <f aca="false">IF(J28&lt;K28,"Reorder Now","OK")</f>
+        <f t="shared" si="1"/>
         <v>Reorder Now</v>
       </c>
-      <c r="M28" s="24" t="n">
-        <f aca="false">IFERROR(I28/(H28+I28),0)</f>
-        <v>0.037037037037037</v>
-      </c>
-      <c r="N28" s="25" t="n">
-        <f aca="false">E28-D28</f>
-        <v>41.68</v>
-      </c>
-      <c r="O28" s="25" t="n">
-        <f aca="false">H28*E28</f>
-        <v>25131.6</v>
-      </c>
-      <c r="P28" s="25" t="n">
-        <f aca="false">I28*D28</f>
+      <c r="M28" s="24">
+        <f t="shared" si="2"/>
+        <v>3.7037037037037035E-2</v>
+      </c>
+      <c r="N28" s="25">
+        <f t="shared" si="3"/>
+        <v>41.679999999999993</v>
+      </c>
+      <c r="O28" s="25">
+        <f t="shared" si="4"/>
+        <v>25131.599999999999</v>
+      </c>
+      <c r="P28" s="25">
+        <f t="shared" si="5"/>
         <v>716.52</v>
       </c>
-      <c r="Q28" s="17" t="n">
-        <f aca="false">RANK(O28,$O$2:$O$44,0)</f>
+      <c r="Q28" s="18">
+        <f t="shared" si="6"/>
         <v>20</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="21" t="n">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A29" s="21">
         <v>28</v>
       </c>
       <c r="B29" s="21" t="s">
@@ -3822,58 +3777,58 @@
       <c r="C29" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="D29" s="22" t="n">
+      <c r="D29" s="22">
         <v>55.54</v>
       </c>
-      <c r="E29" s="22" t="n">
+      <c r="E29" s="22">
         <v>66.37</v>
       </c>
-      <c r="F29" s="21" t="n">
+      <c r="F29" s="21">
         <v>63</v>
       </c>
-      <c r="G29" s="21" t="n">
+      <c r="G29" s="21">
         <v>32</v>
       </c>
-      <c r="H29" s="21" t="n">
+      <c r="H29" s="21">
         <v>61</v>
       </c>
-      <c r="I29" s="21" t="n">
+      <c r="I29" s="21">
         <v>4</v>
       </c>
-      <c r="J29" s="17" t="n">
-        <f aca="false">F29+G29-H29-I29</f>
+      <c r="J29" s="18">
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="K29" s="21" t="n">
+      <c r="K29" s="21">
         <v>33</v>
       </c>
       <c r="L29" s="23" t="str">
-        <f aca="false">IF(J29&lt;K29,"Reorder Now","OK")</f>
+        <f t="shared" si="1"/>
         <v>Reorder Now</v>
       </c>
-      <c r="M29" s="24" t="n">
-        <f aca="false">IFERROR(I29/(H29+I29),0)</f>
-        <v>0.0615384615384615</v>
-      </c>
-      <c r="N29" s="25" t="n">
-        <f aca="false">E29-D29</f>
-        <v>10.83</v>
-      </c>
-      <c r="O29" s="25" t="n">
-        <f aca="false">H29*E29</f>
+      <c r="M29" s="24">
+        <f t="shared" si="2"/>
+        <v>6.1538461538461542E-2</v>
+      </c>
+      <c r="N29" s="25">
+        <f t="shared" si="3"/>
+        <v>10.830000000000005</v>
+      </c>
+      <c r="O29" s="25">
+        <f t="shared" si="4"/>
         <v>4048.57</v>
       </c>
-      <c r="P29" s="25" t="n">
-        <f aca="false">I29*D29</f>
+      <c r="P29" s="25">
+        <f t="shared" si="5"/>
         <v>222.16</v>
       </c>
-      <c r="Q29" s="17" t="n">
-        <f aca="false">RANK(O29,$O$2:$O$44,0)</f>
+      <c r="Q29" s="18">
+        <f t="shared" si="6"/>
         <v>41</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="21" t="n">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A30" s="21">
         <v>29</v>
       </c>
       <c r="B30" s="21" t="s">
@@ -3882,58 +3837,58 @@
       <c r="C30" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="D30" s="22" t="n">
+      <c r="D30" s="22">
         <v>88.77</v>
       </c>
-      <c r="E30" s="22" t="n">
+      <c r="E30" s="22">
         <v>103.35</v>
       </c>
-      <c r="F30" s="21" t="n">
+      <c r="F30" s="21">
         <v>100</v>
       </c>
-      <c r="G30" s="21" t="n">
+      <c r="G30" s="21">
         <v>37</v>
       </c>
-      <c r="H30" s="21" t="n">
+      <c r="H30" s="21">
         <v>125</v>
       </c>
-      <c r="I30" s="21" t="n">
+      <c r="I30" s="21">
         <v>3</v>
       </c>
-      <c r="J30" s="17" t="n">
-        <f aca="false">F30+G30-H30-I30</f>
+      <c r="J30" s="18">
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="K30" s="21" t="n">
+      <c r="K30" s="21">
         <v>16</v>
       </c>
       <c r="L30" s="23" t="str">
-        <f aca="false">IF(J30&lt;K30,"Reorder Now","OK")</f>
+        <f t="shared" si="1"/>
         <v>Reorder Now</v>
       </c>
-      <c r="M30" s="24" t="n">
-        <f aca="false">IFERROR(I30/(H30+I30),0)</f>
-        <v>0.0234375</v>
-      </c>
-      <c r="N30" s="25" t="n">
-        <f aca="false">E30-D30</f>
-        <v>14.58</v>
-      </c>
-      <c r="O30" s="25" t="n">
-        <f aca="false">H30*E30</f>
+      <c r="M30" s="24">
+        <f t="shared" si="2"/>
+        <v>2.34375E-2</v>
+      </c>
+      <c r="N30" s="25">
+        <f t="shared" si="3"/>
+        <v>14.579999999999998</v>
+      </c>
+      <c r="O30" s="25">
+        <f t="shared" si="4"/>
         <v>12918.75</v>
       </c>
-      <c r="P30" s="25" t="n">
-        <f aca="false">I30*D30</f>
+      <c r="P30" s="25">
+        <f t="shared" si="5"/>
         <v>266.31</v>
       </c>
-      <c r="Q30" s="17" t="n">
-        <f aca="false">RANK(O30,$O$2:$O$44,0)</f>
+      <c r="Q30" s="18">
+        <f t="shared" si="6"/>
         <v>32</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="21" t="n">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A31" s="21">
         <v>30</v>
       </c>
       <c r="B31" s="21" t="s">
@@ -3942,58 +3897,58 @@
       <c r="C31" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="D31" s="22" t="n">
+      <c r="D31" s="22">
         <v>302.98</v>
       </c>
-      <c r="E31" s="22" t="n">
+      <c r="E31" s="22">
         <v>352.72</v>
       </c>
-      <c r="F31" s="21" t="n">
+      <c r="F31" s="21">
         <v>50</v>
       </c>
-      <c r="G31" s="21" t="n">
+      <c r="G31" s="21">
         <v>65</v>
       </c>
-      <c r="H31" s="21" t="n">
+      <c r="H31" s="21">
         <v>70</v>
       </c>
-      <c r="I31" s="21" t="n">
+      <c r="I31" s="21">
         <v>5</v>
       </c>
-      <c r="J31" s="17" t="n">
-        <f aca="false">F31+G31-H31-I31</f>
+      <c r="J31" s="18">
+        <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="K31" s="21" t="n">
+      <c r="K31" s="21">
         <v>32</v>
       </c>
       <c r="L31" s="23" t="str">
-        <f aca="false">IF(J31&lt;K31,"Reorder Now","OK")</f>
+        <f t="shared" si="1"/>
         <v>OK</v>
       </c>
-      <c r="M31" s="24" t="n">
-        <f aca="false">IFERROR(I31/(H31+I31),0)</f>
-        <v>0.0666666666666667</v>
-      </c>
-      <c r="N31" s="25" t="n">
-        <f aca="false">E31-D31</f>
-        <v>49.74</v>
-      </c>
-      <c r="O31" s="25" t="n">
-        <f aca="false">H31*E31</f>
-        <v>24690.4</v>
-      </c>
-      <c r="P31" s="25" t="n">
-        <f aca="false">I31*D31</f>
+      <c r="M31" s="24">
+        <f t="shared" si="2"/>
+        <v>6.6666666666666666E-2</v>
+      </c>
+      <c r="N31" s="25">
+        <f t="shared" si="3"/>
+        <v>49.740000000000009</v>
+      </c>
+      <c r="O31" s="25">
+        <f t="shared" si="4"/>
+        <v>24690.400000000001</v>
+      </c>
+      <c r="P31" s="25">
+        <f t="shared" si="5"/>
         <v>1514.9</v>
       </c>
-      <c r="Q31" s="17" t="n">
-        <f aca="false">RANK(O31,$O$2:$O$44,0)</f>
+      <c r="Q31" s="18">
+        <f t="shared" si="6"/>
         <v>21</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="21" t="n">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A32" s="21">
         <v>31</v>
       </c>
       <c r="B32" s="21" t="s">
@@ -4002,58 +3957,58 @@
       <c r="C32" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="D32" s="22" t="n">
+      <c r="D32" s="22">
         <v>59.32</v>
       </c>
-      <c r="E32" s="22" t="n">
-        <v>79.32</v>
-      </c>
-      <c r="F32" s="21" t="n">
+      <c r="E32" s="22">
+        <v>79.319999999999993</v>
+      </c>
+      <c r="F32" s="21">
         <v>93</v>
       </c>
-      <c r="G32" s="21" t="n">
+      <c r="G32" s="21">
         <v>103</v>
       </c>
-      <c r="H32" s="21" t="n">
+      <c r="H32" s="21">
         <v>158</v>
       </c>
-      <c r="I32" s="21" t="n">
+      <c r="I32" s="21">
         <v>7</v>
       </c>
-      <c r="J32" s="17" t="n">
-        <f aca="false">F32+G32-H32-I32</f>
+      <c r="J32" s="18">
+        <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="K32" s="21" t="n">
+      <c r="K32" s="21">
         <v>40</v>
       </c>
       <c r="L32" s="23" t="str">
-        <f aca="false">IF(J32&lt;K32,"Reorder Now","OK")</f>
+        <f t="shared" si="1"/>
         <v>Reorder Now</v>
       </c>
-      <c r="M32" s="24" t="n">
-        <f aca="false">IFERROR(I32/(H32+I32),0)</f>
-        <v>0.0424242424242424</v>
-      </c>
-      <c r="N32" s="25" t="n">
-        <f aca="false">E32-D32</f>
-        <v>20</v>
-      </c>
-      <c r="O32" s="25" t="n">
-        <f aca="false">H32*E32</f>
+      <c r="M32" s="24">
+        <f t="shared" si="2"/>
+        <v>4.2424242424242427E-2</v>
+      </c>
+      <c r="N32" s="25">
+        <f t="shared" si="3"/>
+        <v>19.999999999999993</v>
+      </c>
+      <c r="O32" s="25">
+        <f t="shared" si="4"/>
         <v>12532.56</v>
       </c>
-      <c r="P32" s="25" t="n">
-        <f aca="false">I32*D32</f>
+      <c r="P32" s="25">
+        <f t="shared" si="5"/>
         <v>415.24</v>
       </c>
-      <c r="Q32" s="17" t="n">
-        <f aca="false">RANK(O32,$O$2:$O$44,0)</f>
+      <c r="Q32" s="18">
+        <f t="shared" si="6"/>
         <v>34</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="21" t="n">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A33" s="21">
         <v>32</v>
       </c>
       <c r="B33" s="21" t="s">
@@ -4062,58 +4017,58 @@
       <c r="C33" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="D33" s="22" t="n">
+      <c r="D33" s="22">
         <v>151.37</v>
       </c>
-      <c r="E33" s="22" t="n">
+      <c r="E33" s="22">
         <v>176.93</v>
       </c>
-      <c r="F33" s="21" t="n">
+      <c r="F33" s="21">
         <v>104</v>
       </c>
-      <c r="G33" s="21" t="n">
+      <c r="G33" s="21">
         <v>85</v>
       </c>
-      <c r="H33" s="21" t="n">
+      <c r="H33" s="21">
         <v>146</v>
       </c>
-      <c r="I33" s="21" t="n">
+      <c r="I33" s="21">
         <v>5</v>
       </c>
-      <c r="J33" s="17" t="n">
-        <f aca="false">F33+G33-H33-I33</f>
+      <c r="J33" s="18">
+        <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="K33" s="21" t="n">
+      <c r="K33" s="21">
         <v>29</v>
       </c>
       <c r="L33" s="23" t="str">
-        <f aca="false">IF(J33&lt;K33,"Reorder Now","OK")</f>
+        <f t="shared" si="1"/>
         <v>OK</v>
       </c>
-      <c r="M33" s="24" t="n">
-        <f aca="false">IFERROR(I33/(H33+I33),0)</f>
-        <v>0.033112582781457</v>
-      </c>
-      <c r="N33" s="25" t="n">
-        <f aca="false">E33-D33</f>
-        <v>25.56</v>
-      </c>
-      <c r="O33" s="25" t="n">
-        <f aca="false">H33*E33</f>
-        <v>25831.78</v>
-      </c>
-      <c r="P33" s="25" t="n">
-        <f aca="false">I33*D33</f>
+      <c r="M33" s="24">
+        <f t="shared" si="2"/>
+        <v>3.3112582781456956E-2</v>
+      </c>
+      <c r="N33" s="25">
+        <f t="shared" si="3"/>
+        <v>25.560000000000002</v>
+      </c>
+      <c r="O33" s="25">
+        <f t="shared" si="4"/>
+        <v>25831.780000000002</v>
+      </c>
+      <c r="P33" s="25">
+        <f t="shared" si="5"/>
         <v>756.85</v>
       </c>
-      <c r="Q33" s="17" t="n">
-        <f aca="false">RANK(O33,$O$2:$O$44,0)</f>
+      <c r="Q33" s="18">
+        <f t="shared" si="6"/>
         <v>19</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="21" t="n">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A34" s="21">
         <v>33</v>
       </c>
       <c r="B34" s="21" t="s">
@@ -4122,58 +4077,58 @@
       <c r="C34" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="D34" s="22" t="n">
+      <c r="D34" s="22">
         <v>304.39</v>
       </c>
-      <c r="E34" s="22" t="n">
+      <c r="E34" s="22">
         <v>353.35</v>
       </c>
-      <c r="F34" s="21" t="n">
+      <c r="F34" s="21">
         <v>103</v>
       </c>
-      <c r="G34" s="21" t="n">
+      <c r="G34" s="21">
         <v>112</v>
       </c>
-      <c r="H34" s="21" t="n">
+      <c r="H34" s="21">
         <v>158</v>
       </c>
-      <c r="I34" s="21" t="n">
+      <c r="I34" s="21">
         <v>3</v>
       </c>
-      <c r="J34" s="17" t="n">
-        <f aca="false">F34+G34-H34-I34</f>
+      <c r="J34" s="18">
+        <f t="shared" si="0"/>
         <v>54</v>
       </c>
-      <c r="K34" s="21" t="n">
+      <c r="K34" s="21">
         <v>38</v>
       </c>
       <c r="L34" s="23" t="str">
-        <f aca="false">IF(J34&lt;K34,"Reorder Now","OK")</f>
+        <f t="shared" si="1"/>
         <v>OK</v>
       </c>
-      <c r="M34" s="24" t="n">
-        <f aca="false">IFERROR(I34/(H34+I34),0)</f>
-        <v>0.0186335403726708</v>
-      </c>
-      <c r="N34" s="25" t="n">
-        <f aca="false">E34-D34</f>
-        <v>48.96</v>
-      </c>
-      <c r="O34" s="25" t="n">
-        <f aca="false">H34*E34</f>
+      <c r="M34" s="24">
+        <f t="shared" si="2"/>
+        <v>1.8633540372670808E-2</v>
+      </c>
+      <c r="N34" s="25">
+        <f t="shared" si="3"/>
+        <v>48.960000000000036</v>
+      </c>
+      <c r="O34" s="25">
+        <f t="shared" si="4"/>
         <v>55829.3</v>
       </c>
-      <c r="P34" s="25" t="n">
-        <f aca="false">I34*D34</f>
+      <c r="P34" s="25">
+        <f t="shared" si="5"/>
         <v>913.17</v>
       </c>
-      <c r="Q34" s="17" t="n">
-        <f aca="false">RANK(O34,$O$2:$O$44,0)</f>
+      <c r="Q34" s="18">
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="21" t="n">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A35" s="21">
         <v>34</v>
       </c>
       <c r="B35" s="21" t="s">
@@ -4182,58 +4137,58 @@
       <c r="C35" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="D35" s="22" t="n">
-        <v>128.67</v>
-      </c>
-      <c r="E35" s="22" t="n">
+      <c r="D35" s="22">
+        <v>128.66999999999999</v>
+      </c>
+      <c r="E35" s="22">
         <v>170.14</v>
       </c>
-      <c r="F35" s="21" t="n">
+      <c r="F35" s="21">
         <v>51</v>
       </c>
-      <c r="G35" s="21" t="n">
+      <c r="G35" s="21">
         <v>54</v>
       </c>
-      <c r="H35" s="21" t="n">
+      <c r="H35" s="21">
         <v>80</v>
       </c>
-      <c r="I35" s="21" t="n">
+      <c r="I35" s="21">
         <v>2</v>
       </c>
-      <c r="J35" s="17" t="n">
-        <f aca="false">F35+G35-H35-I35</f>
+      <c r="J35" s="18">
+        <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="K35" s="21" t="n">
+      <c r="K35" s="21">
         <v>19</v>
       </c>
       <c r="L35" s="23" t="str">
-        <f aca="false">IF(J35&lt;K35,"Reorder Now","OK")</f>
+        <f t="shared" si="1"/>
         <v>OK</v>
       </c>
-      <c r="M35" s="24" t="n">
-        <f aca="false">IFERROR(I35/(H35+I35),0)</f>
-        <v>0.024390243902439</v>
-      </c>
-      <c r="N35" s="25" t="n">
-        <f aca="false">E35-D35</f>
+      <c r="M35" s="24">
+        <f t="shared" si="2"/>
+        <v>2.4390243902439025E-2</v>
+      </c>
+      <c r="N35" s="25">
+        <f t="shared" si="3"/>
         <v>41.47</v>
       </c>
-      <c r="O35" s="25" t="n">
-        <f aca="false">H35*E35</f>
-        <v>13611.2</v>
-      </c>
-      <c r="P35" s="25" t="n">
-        <f aca="false">I35*D35</f>
-        <v>257.34</v>
-      </c>
-      <c r="Q35" s="17" t="n">
-        <f aca="false">RANK(O35,$O$2:$O$44,0)</f>
+      <c r="O35" s="25">
+        <f t="shared" si="4"/>
+        <v>13611.199999999999</v>
+      </c>
+      <c r="P35" s="25">
+        <f t="shared" si="5"/>
+        <v>257.33999999999997</v>
+      </c>
+      <c r="Q35" s="18">
+        <f t="shared" si="6"/>
         <v>30</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="21" t="n">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A36" s="21">
         <v>35</v>
       </c>
       <c r="B36" s="21" t="s">
@@ -4242,58 +4197,58 @@
       <c r="C36" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="D36" s="22" t="n">
-        <v>156.33</v>
-      </c>
-      <c r="E36" s="22" t="n">
+      <c r="D36" s="22">
+        <v>156.33000000000001</v>
+      </c>
+      <c r="E36" s="22">
         <v>188.49</v>
       </c>
-      <c r="F36" s="21" t="n">
+      <c r="F36" s="21">
         <v>51</v>
       </c>
-      <c r="G36" s="21" t="n">
+      <c r="G36" s="21">
         <v>141</v>
       </c>
-      <c r="H36" s="21" t="n">
+      <c r="H36" s="21">
         <v>152</v>
       </c>
-      <c r="I36" s="21" t="n">
+      <c r="I36" s="21">
         <v>12</v>
       </c>
-      <c r="J36" s="17" t="n">
-        <f aca="false">F36+G36-H36-I36</f>
+      <c r="J36" s="18">
+        <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="K36" s="21" t="n">
+      <c r="K36" s="21">
         <v>40</v>
       </c>
       <c r="L36" s="23" t="str">
-        <f aca="false">IF(J36&lt;K36,"Reorder Now","OK")</f>
+        <f t="shared" si="1"/>
         <v>Reorder Now</v>
       </c>
-      <c r="M36" s="24" t="n">
-        <f aca="false">IFERROR(I36/(H36+I36),0)</f>
-        <v>0.0731707317073171</v>
-      </c>
-      <c r="N36" s="25" t="n">
-        <f aca="false">E36-D36</f>
-        <v>32.16</v>
-      </c>
-      <c r="O36" s="25" t="n">
-        <f aca="false">H36*E36</f>
-        <v>28650.48</v>
-      </c>
-      <c r="P36" s="25" t="n">
-        <f aca="false">I36*D36</f>
+      <c r="M36" s="24">
+        <f t="shared" si="2"/>
+        <v>7.3170731707317069E-2</v>
+      </c>
+      <c r="N36" s="25">
+        <f t="shared" si="3"/>
+        <v>32.159999999999997</v>
+      </c>
+      <c r="O36" s="25">
+        <f t="shared" si="4"/>
+        <v>28650.480000000003</v>
+      </c>
+      <c r="P36" s="25">
+        <f t="shared" si="5"/>
         <v>1875.96</v>
       </c>
-      <c r="Q36" s="17" t="n">
-        <f aca="false">RANK(O36,$O$2:$O$44,0)</f>
+      <c r="Q36" s="18">
+        <f t="shared" si="6"/>
         <v>17</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="21" t="n">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A37" s="21">
         <v>36</v>
       </c>
       <c r="B37" s="21" t="s">
@@ -4302,58 +4257,58 @@
       <c r="C37" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="D37" s="22" t="n">
+      <c r="D37" s="22">
         <v>303.55</v>
       </c>
-      <c r="E37" s="22" t="n">
+      <c r="E37" s="22">
         <v>382.49</v>
       </c>
-      <c r="F37" s="21" t="n">
+      <c r="F37" s="21">
         <v>26</v>
       </c>
-      <c r="G37" s="21" t="n">
+      <c r="G37" s="21">
         <v>113</v>
       </c>
-      <c r="H37" s="21" t="n">
+      <c r="H37" s="21">
         <v>122</v>
       </c>
-      <c r="I37" s="21" t="n">
+      <c r="I37" s="21">
         <v>9</v>
       </c>
-      <c r="J37" s="17" t="n">
-        <f aca="false">F37+G37-H37-I37</f>
+      <c r="J37" s="18">
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="K37" s="21" t="n">
+      <c r="K37" s="21">
         <v>15</v>
       </c>
       <c r="L37" s="23" t="str">
-        <f aca="false">IF(J37&lt;K37,"Reorder Now","OK")</f>
+        <f t="shared" si="1"/>
         <v>Reorder Now</v>
       </c>
-      <c r="M37" s="24" t="n">
-        <f aca="false">IFERROR(I37/(H37+I37),0)</f>
-        <v>0.0687022900763359</v>
-      </c>
-      <c r="N37" s="25" t="n">
-        <f aca="false">E37-D37</f>
+      <c r="M37" s="24">
+        <f t="shared" si="2"/>
+        <v>6.8702290076335881E-2</v>
+      </c>
+      <c r="N37" s="25">
+        <f t="shared" si="3"/>
         <v>78.94</v>
       </c>
-      <c r="O37" s="25" t="n">
-        <f aca="false">H37*E37</f>
+      <c r="O37" s="25">
+        <f t="shared" si="4"/>
         <v>46663.78</v>
       </c>
-      <c r="P37" s="25" t="n">
-        <f aca="false">I37*D37</f>
-        <v>2731.95</v>
-      </c>
-      <c r="Q37" s="17" t="n">
-        <f aca="false">RANK(O37,$O$2:$O$44,0)</f>
+      <c r="P37" s="25">
+        <f t="shared" si="5"/>
+        <v>2731.9500000000003</v>
+      </c>
+      <c r="Q37" s="18">
+        <f t="shared" si="6"/>
         <v>7</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="21" t="n">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A38" s="21">
         <v>37</v>
       </c>
       <c r="B38" s="21" t="s">
@@ -4362,58 +4317,58 @@
       <c r="C38" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="D38" s="22" t="n">
+      <c r="D38" s="22">
         <v>339.61</v>
       </c>
-      <c r="E38" s="22" t="n">
+      <c r="E38" s="22">
         <v>453.47</v>
       </c>
-      <c r="F38" s="21" t="n">
+      <c r="F38" s="21">
         <v>50</v>
       </c>
-      <c r="G38" s="21" t="n">
+      <c r="G38" s="21">
         <v>51</v>
       </c>
-      <c r="H38" s="21" t="n">
+      <c r="H38" s="21">
         <v>80</v>
       </c>
-      <c r="I38" s="21" t="n">
+      <c r="I38" s="21">
         <v>3</v>
       </c>
-      <c r="J38" s="17" t="n">
-        <f aca="false">F38+G38-H38-I38</f>
+      <c r="J38" s="18">
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="K38" s="21" t="n">
+      <c r="K38" s="21">
         <v>21</v>
       </c>
       <c r="L38" s="23" t="str">
-        <f aca="false">IF(J38&lt;K38,"Reorder Now","OK")</f>
+        <f t="shared" si="1"/>
         <v>Reorder Now</v>
       </c>
-      <c r="M38" s="24" t="n">
-        <f aca="false">IFERROR(I38/(H38+I38),0)</f>
-        <v>0.036144578313253</v>
-      </c>
-      <c r="N38" s="25" t="n">
-        <f aca="false">E38-D38</f>
-        <v>113.86</v>
-      </c>
-      <c r="O38" s="25" t="n">
-        <f aca="false">H38*E38</f>
-        <v>36277.6</v>
-      </c>
-      <c r="P38" s="25" t="n">
-        <f aca="false">I38*D38</f>
+      <c r="M38" s="24">
+        <f t="shared" si="2"/>
+        <v>3.614457831325301E-2</v>
+      </c>
+      <c r="N38" s="25">
+        <f t="shared" si="3"/>
+        <v>113.86000000000001</v>
+      </c>
+      <c r="O38" s="25">
+        <f t="shared" si="4"/>
+        <v>36277.600000000006</v>
+      </c>
+      <c r="P38" s="25">
+        <f t="shared" si="5"/>
         <v>1018.83</v>
       </c>
-      <c r="Q38" s="17" t="n">
-        <f aca="false">RANK(O38,$O$2:$O$44,0)</f>
+      <c r="Q38" s="18">
+        <f t="shared" si="6"/>
         <v>9</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="21" t="n">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A39" s="21">
         <v>38</v>
       </c>
       <c r="B39" s="21" t="s">
@@ -4422,58 +4377,58 @@
       <c r="C39" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="D39" s="22" t="n">
-        <v>304.66</v>
-      </c>
-      <c r="E39" s="22" t="n">
+      <c r="D39" s="22">
+        <v>304.66000000000003</v>
+      </c>
+      <c r="E39" s="22">
         <v>405.35</v>
       </c>
-      <c r="F39" s="21" t="n">
+      <c r="F39" s="21">
         <v>41</v>
       </c>
-      <c r="G39" s="21" t="n">
+      <c r="G39" s="21">
         <v>78</v>
       </c>
-      <c r="H39" s="21" t="n">
+      <c r="H39" s="21">
         <v>83</v>
       </c>
-      <c r="I39" s="21" t="n">
+      <c r="I39" s="21">
         <v>1</v>
       </c>
-      <c r="J39" s="17" t="n">
-        <f aca="false">F39+G39-H39-I39</f>
+      <c r="J39" s="18">
+        <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="K39" s="21" t="n">
+      <c r="K39" s="21">
         <v>23</v>
       </c>
       <c r="L39" s="23" t="str">
-        <f aca="false">IF(J39&lt;K39,"Reorder Now","OK")</f>
+        <f t="shared" si="1"/>
         <v>OK</v>
       </c>
-      <c r="M39" s="24" t="n">
-        <f aca="false">IFERROR(I39/(H39+I39),0)</f>
-        <v>0.0119047619047619</v>
-      </c>
-      <c r="N39" s="25" t="n">
-        <f aca="false">E39-D39</f>
+      <c r="M39" s="24">
+        <f t="shared" si="2"/>
+        <v>1.1904761904761904E-2</v>
+      </c>
+      <c r="N39" s="25">
+        <f t="shared" si="3"/>
         <v>100.69</v>
       </c>
-      <c r="O39" s="25" t="n">
-        <f aca="false">H39*E39</f>
-        <v>33644.05</v>
-      </c>
-      <c r="P39" s="25" t="n">
-        <f aca="false">I39*D39</f>
-        <v>304.66</v>
-      </c>
-      <c r="Q39" s="17" t="n">
-        <f aca="false">RANK(O39,$O$2:$O$44,0)</f>
+      <c r="O39" s="25">
+        <f t="shared" si="4"/>
+        <v>33644.050000000003</v>
+      </c>
+      <c r="P39" s="25">
+        <f t="shared" si="5"/>
+        <v>304.66000000000003</v>
+      </c>
+      <c r="Q39" s="18">
+        <f t="shared" si="6"/>
         <v>11</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="21" t="n">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A40" s="21">
         <v>39</v>
       </c>
       <c r="B40" s="21" t="s">
@@ -4482,58 +4437,58 @@
       <c r="C40" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="D40" s="22" t="n">
+      <c r="D40" s="22">
         <v>325.38</v>
       </c>
-      <c r="E40" s="22" t="n">
+      <c r="E40" s="22">
         <v>425.28</v>
       </c>
-      <c r="F40" s="21" t="n">
+      <c r="F40" s="21">
         <v>56</v>
       </c>
-      <c r="G40" s="21" t="n">
+      <c r="G40" s="21">
         <v>84</v>
       </c>
-      <c r="H40" s="21" t="n">
+      <c r="H40" s="21">
         <v>116</v>
       </c>
-      <c r="I40" s="21" t="n">
+      <c r="I40" s="21">
         <v>7</v>
       </c>
-      <c r="J40" s="17" t="n">
-        <f aca="false">F40+G40-H40-I40</f>
+      <c r="J40" s="18">
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="K40" s="21" t="n">
+      <c r="K40" s="21">
         <v>40</v>
       </c>
       <c r="L40" s="23" t="str">
-        <f aca="false">IF(J40&lt;K40,"Reorder Now","OK")</f>
+        <f t="shared" si="1"/>
         <v>Reorder Now</v>
       </c>
-      <c r="M40" s="24" t="n">
-        <f aca="false">IFERROR(I40/(H40+I40),0)</f>
-        <v>0.0569105691056911</v>
-      </c>
-      <c r="N40" s="25" t="n">
-        <f aca="false">E40-D40</f>
-        <v>99.9</v>
-      </c>
-      <c r="O40" s="25" t="n">
-        <f aca="false">H40*E40</f>
-        <v>49332.48</v>
-      </c>
-      <c r="P40" s="25" t="n">
-        <f aca="false">I40*D40</f>
+      <c r="M40" s="24">
+        <f t="shared" si="2"/>
+        <v>5.6910569105691054E-2</v>
+      </c>
+      <c r="N40" s="25">
+        <f t="shared" si="3"/>
+        <v>99.899999999999977</v>
+      </c>
+      <c r="O40" s="25">
+        <f t="shared" si="4"/>
+        <v>49332.479999999996</v>
+      </c>
+      <c r="P40" s="25">
+        <f t="shared" si="5"/>
         <v>2277.66</v>
       </c>
-      <c r="Q40" s="17" t="n">
-        <f aca="false">RANK(O40,$O$2:$O$44,0)</f>
+      <c r="Q40" s="18">
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="21" t="n">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A41" s="21">
         <v>40</v>
       </c>
       <c r="B41" s="21" t="s">
@@ -4542,58 +4497,58 @@
       <c r="C41" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="D41" s="22" t="n">
+      <c r="D41" s="22">
         <v>201.18</v>
       </c>
-      <c r="E41" s="22" t="n">
+      <c r="E41" s="22">
         <v>260.26</v>
       </c>
-      <c r="F41" s="21" t="n">
+      <c r="F41" s="21">
         <v>39</v>
       </c>
-      <c r="G41" s="21" t="n">
+      <c r="G41" s="21">
         <v>54</v>
       </c>
-      <c r="H41" s="21" t="n">
+      <c r="H41" s="21">
         <v>49</v>
       </c>
-      <c r="I41" s="21" t="n">
+      <c r="I41" s="21">
         <v>2</v>
       </c>
-      <c r="J41" s="17" t="n">
-        <f aca="false">F41+G41-H41-I41</f>
+      <c r="J41" s="18">
+        <f t="shared" si="0"/>
         <v>42</v>
       </c>
-      <c r="K41" s="21" t="n">
+      <c r="K41" s="21">
         <v>33</v>
       </c>
       <c r="L41" s="23" t="str">
-        <f aca="false">IF(J41&lt;K41,"Reorder Now","OK")</f>
+        <f t="shared" si="1"/>
         <v>OK</v>
       </c>
-      <c r="M41" s="24" t="n">
-        <f aca="false">IFERROR(I41/(H41+I41),0)</f>
-        <v>0.0392156862745098</v>
-      </c>
-      <c r="N41" s="25" t="n">
-        <f aca="false">E41-D41</f>
-        <v>59.08</v>
-      </c>
-      <c r="O41" s="25" t="n">
-        <f aca="false">H41*E41</f>
+      <c r="M41" s="24">
+        <f t="shared" si="2"/>
+        <v>3.9215686274509803E-2</v>
+      </c>
+      <c r="N41" s="25">
+        <f t="shared" si="3"/>
+        <v>59.079999999999984</v>
+      </c>
+      <c r="O41" s="25">
+        <f t="shared" si="4"/>
         <v>12752.74</v>
       </c>
-      <c r="P41" s="25" t="n">
-        <f aca="false">I41*D41</f>
+      <c r="P41" s="25">
+        <f t="shared" si="5"/>
         <v>402.36</v>
       </c>
-      <c r="Q41" s="17" t="n">
-        <f aca="false">RANK(O41,$O$2:$O$44,0)</f>
+      <c r="Q41" s="18">
+        <f t="shared" si="6"/>
         <v>33</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="21" t="n">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A42" s="21">
         <v>41</v>
       </c>
       <c r="B42" s="21" t="s">
@@ -4602,58 +4557,58 @@
       <c r="C42" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="D42" s="22" t="n">
-        <v>261.47</v>
-      </c>
-      <c r="E42" s="22" t="n">
+      <c r="D42" s="22">
+        <v>261.47000000000003</v>
+      </c>
+      <c r="E42" s="22">
         <v>303.88</v>
       </c>
-      <c r="F42" s="21" t="n">
+      <c r="F42" s="21">
         <v>60</v>
       </c>
-      <c r="G42" s="21" t="n">
+      <c r="G42" s="21">
         <v>37</v>
       </c>
-      <c r="H42" s="21" t="n">
+      <c r="H42" s="21">
         <v>78</v>
       </c>
-      <c r="I42" s="21" t="n">
+      <c r="I42" s="21">
         <v>1</v>
       </c>
-      <c r="J42" s="17" t="n">
-        <f aca="false">F42+G42-H42-I42</f>
+      <c r="J42" s="18">
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="K42" s="21" t="n">
+      <c r="K42" s="21">
         <v>31</v>
       </c>
       <c r="L42" s="23" t="str">
-        <f aca="false">IF(J42&lt;K42,"Reorder Now","OK")</f>
+        <f t="shared" si="1"/>
         <v>Reorder Now</v>
       </c>
-      <c r="M42" s="24" t="n">
-        <f aca="false">IFERROR(I42/(H42+I42),0)</f>
-        <v>0.0126582278481013</v>
-      </c>
-      <c r="N42" s="25" t="n">
-        <f aca="false">E42-D42</f>
-        <v>42.41</v>
-      </c>
-      <c r="O42" s="25" t="n">
-        <f aca="false">H42*E42</f>
-        <v>23702.64</v>
-      </c>
-      <c r="P42" s="25" t="n">
-        <f aca="false">I42*D42</f>
-        <v>261.47</v>
-      </c>
-      <c r="Q42" s="17" t="n">
-        <f aca="false">RANK(O42,$O$2:$O$44,0)</f>
+      <c r="M42" s="24">
+        <f t="shared" si="2"/>
+        <v>1.2658227848101266E-2</v>
+      </c>
+      <c r="N42" s="25">
+        <f t="shared" si="3"/>
+        <v>42.409999999999968</v>
+      </c>
+      <c r="O42" s="25">
+        <f t="shared" si="4"/>
+        <v>23702.639999999999</v>
+      </c>
+      <c r="P42" s="25">
+        <f t="shared" si="5"/>
+        <v>261.47000000000003</v>
+      </c>
+      <c r="Q42" s="18">
+        <f t="shared" si="6"/>
         <v>23</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="21" t="n">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A43" s="21">
         <v>42</v>
       </c>
       <c r="B43" s="21" t="s">
@@ -4662,58 +4617,58 @@
       <c r="C43" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="D43" s="22" t="n">
+      <c r="D43" s="22">
         <v>322.99</v>
       </c>
-      <c r="E43" s="22" t="n">
+      <c r="E43" s="22">
         <v>405.75</v>
       </c>
-      <c r="F43" s="21" t="n">
+      <c r="F43" s="21">
         <v>27</v>
       </c>
-      <c r="G43" s="21" t="n">
+      <c r="G43" s="21">
         <v>95</v>
       </c>
-      <c r="H43" s="21" t="n">
+      <c r="H43" s="21">
         <v>72</v>
       </c>
-      <c r="I43" s="21" t="n">
+      <c r="I43" s="21">
         <v>1</v>
       </c>
-      <c r="J43" s="17" t="n">
-        <f aca="false">F43+G43-H43-I43</f>
+      <c r="J43" s="18">
+        <f t="shared" si="0"/>
         <v>49</v>
       </c>
-      <c r="K43" s="21" t="n">
+      <c r="K43" s="21">
         <v>17</v>
       </c>
       <c r="L43" s="23" t="str">
-        <f aca="false">IF(J43&lt;K43,"Reorder Now","OK")</f>
+        <f t="shared" si="1"/>
         <v>OK</v>
       </c>
-      <c r="M43" s="24" t="n">
-        <f aca="false">IFERROR(I43/(H43+I43),0)</f>
-        <v>0.0136986301369863</v>
-      </c>
-      <c r="N43" s="25" t="n">
-        <f aca="false">E43-D43</f>
-        <v>82.76</v>
-      </c>
-      <c r="O43" s="25" t="n">
-        <f aca="false">H43*E43</f>
+      <c r="M43" s="24">
+        <f t="shared" si="2"/>
+        <v>1.3698630136986301E-2</v>
+      </c>
+      <c r="N43" s="25">
+        <f t="shared" si="3"/>
+        <v>82.759999999999991</v>
+      </c>
+      <c r="O43" s="25">
+        <f t="shared" si="4"/>
         <v>29214</v>
       </c>
-      <c r="P43" s="25" t="n">
-        <f aca="false">I43*D43</f>
+      <c r="P43" s="25">
+        <f t="shared" si="5"/>
         <v>322.99</v>
       </c>
-      <c r="Q43" s="17" t="n">
-        <f aca="false">RANK(O43,$O$2:$O$44,0)</f>
+      <c r="Q43" s="18">
+        <f t="shared" si="6"/>
         <v>16</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="21" t="n">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A44" s="21">
         <v>43</v>
       </c>
       <c r="B44" s="21" t="s">
@@ -4722,91 +4677,83 @@
       <c r="C44" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="D44" s="22" t="n">
+      <c r="D44" s="22">
         <v>214.34</v>
       </c>
-      <c r="E44" s="22" t="n">
+      <c r="E44" s="22">
         <v>275.44</v>
       </c>
-      <c r="F44" s="21" t="n">
+      <c r="F44" s="21">
         <v>50</v>
       </c>
-      <c r="G44" s="21" t="n">
+      <c r="G44" s="21">
         <v>81</v>
       </c>
-      <c r="H44" s="21" t="n">
+      <c r="H44" s="21">
         <v>121</v>
       </c>
-      <c r="I44" s="21" t="n">
+      <c r="I44" s="21">
         <v>2</v>
       </c>
-      <c r="J44" s="17" t="n">
-        <f aca="false">F44+G44-H44-I44</f>
+      <c r="J44" s="18">
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="K44" s="21" t="n">
+      <c r="K44" s="21">
         <v>33</v>
       </c>
       <c r="L44" s="23" t="str">
-        <f aca="false">IF(J44&lt;K44,"Reorder Now","OK")</f>
+        <f t="shared" si="1"/>
         <v>Reorder Now</v>
       </c>
-      <c r="M44" s="24" t="n">
-        <f aca="false">IFERROR(I44/(H44+I44),0)</f>
-        <v>0.016260162601626</v>
-      </c>
-      <c r="N44" s="25" t="n">
-        <f aca="false">E44-D44</f>
-        <v>61.1</v>
-      </c>
-      <c r="O44" s="25" t="n">
-        <f aca="false">H44*E44</f>
-        <v>33328.24</v>
-      </c>
-      <c r="P44" s="25" t="n">
-        <f aca="false">I44*D44</f>
+      <c r="M44" s="24">
+        <f t="shared" si="2"/>
+        <v>1.6260162601626018E-2</v>
+      </c>
+      <c r="N44" s="25">
+        <f t="shared" si="3"/>
+        <v>61.099999999999994</v>
+      </c>
+      <c r="O44" s="25">
+        <f t="shared" si="4"/>
+        <v>33328.239999999998</v>
+      </c>
+      <c r="P44" s="25">
+        <f t="shared" si="5"/>
         <v>428.68</v>
       </c>
-      <c r="Q44" s="17" t="n">
-        <f aca="false">RANK(O44,$O$2:$O$44,0)</f>
+      <c r="Q44" s="18">
+        <f t="shared" si="6"/>
         <v>12</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="L2:L44">
-    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>"Reorder Now"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
       <formula>"OK"</formula>
     </cfRule>
   </conditionalFormatting>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:F8"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="5" width="20" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="20" t="s">
         <v>36</v>
       </c>
@@ -4826,188 +4773,183 @@
         <v>44</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="B2" s="17" t="n">
-        <f aca="false">SUMIFS(Raw_Data!$H$2:$H$44,Raw_Data!$C$2:$C$44,A2)</f>
+      <c r="B2" s="18">
+        <f>SUMIFS(Raw_Data!$H$2:$H$44,Raw_Data!$C$2:$C$44,A2)</f>
         <v>663</v>
       </c>
-      <c r="C2" s="17" t="n">
-        <f aca="false">SUMIFS(Raw_Data!$I$2:$I$44,Raw_Data!$C$2:$C$44,A2)</f>
+      <c r="C2" s="18">
+        <f>SUMIFS(Raw_Data!$I$2:$I$44,Raw_Data!$C$2:$C$44,A2)</f>
         <v>120</v>
       </c>
-      <c r="D2" s="18" t="n">
-        <f aca="false">SUMIFS(Raw_Data!$O$2:$O$44,Raw_Data!$C$2:$C$44,A2)</f>
+      <c r="D2" s="19">
+        <f>SUMIFS(Raw_Data!$O$2:$O$44,Raw_Data!$C$2:$C$44,A2)</f>
         <v>117571.7</v>
       </c>
-      <c r="E2" s="18" t="n">
-        <f aca="false">SUMIFS(Raw_Data!$P$2:$P$44,Raw_Data!$C$2:$C$44,A2)</f>
-        <v>16950.31</v>
-      </c>
-      <c r="F2" s="24" t="n">
-        <f aca="false">IFERROR(C2/(B2+C2),0)</f>
-        <v>0.153256704980843</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E2" s="19">
+        <f>SUMIFS(Raw_Data!$P$2:$P$44,Raw_Data!$C$2:$C$44,A2)</f>
+        <v>16950.309999999998</v>
+      </c>
+      <c r="F2" s="24">
+        <f t="shared" ref="F2:F8" si="0">IFERROR(C2/(B2+C2),0)</f>
+        <v>0.1532567049808429</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="B3" s="17" t="n">
-        <f aca="false">SUMIFS(Raw_Data!$H$2:$H$44,Raw_Data!$C$2:$C$44,A3)</f>
+      <c r="B3" s="18">
+        <f>SUMIFS(Raw_Data!$H$2:$H$44,Raw_Data!$C$2:$C$44,A3)</f>
         <v>821</v>
       </c>
-      <c r="C3" s="17" t="n">
-        <f aca="false">SUMIFS(Raw_Data!$I$2:$I$44,Raw_Data!$C$2:$C$44,A3)</f>
+      <c r="C3" s="18">
+        <f>SUMIFS(Raw_Data!$I$2:$I$44,Raw_Data!$C$2:$C$44,A3)</f>
         <v>54</v>
       </c>
-      <c r="D3" s="18" t="n">
-        <f aca="false">SUMIFS(Raw_Data!$O$2:$O$44,Raw_Data!$C$2:$C$44,A3)</f>
+      <c r="D3" s="19">
+        <f>SUMIFS(Raw_Data!$O$2:$O$44,Raw_Data!$C$2:$C$44,A3)</f>
         <v>240021.43</v>
       </c>
-      <c r="E3" s="18" t="n">
-        <f aca="false">SUMIFS(Raw_Data!$P$2:$P$44,Raw_Data!$C$2:$C$44,A3)</f>
-        <v>11340.78</v>
-      </c>
-      <c r="F3" s="24" t="n">
-        <f aca="false">IFERROR(C3/(B3+C3),0)</f>
-        <v>0.0617142857142857</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E3" s="19">
+        <f>SUMIFS(Raw_Data!$P$2:$P$44,Raw_Data!$C$2:$C$44,A3)</f>
+        <v>11340.779999999999</v>
+      </c>
+      <c r="F3" s="24">
+        <f t="shared" si="0"/>
+        <v>6.1714285714285715E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="B4" s="17" t="n">
-        <f aca="false">SUMIFS(Raw_Data!$H$2:$H$44,Raw_Data!$C$2:$C$44,A4)</f>
+      <c r="B4" s="18">
+        <f>SUMIFS(Raw_Data!$H$2:$H$44,Raw_Data!$C$2:$C$44,A4)</f>
         <v>904</v>
       </c>
-      <c r="C4" s="17" t="n">
-        <f aca="false">SUMIFS(Raw_Data!$I$2:$I$44,Raw_Data!$C$2:$C$44,A4)</f>
+      <c r="C4" s="18">
+        <f>SUMIFS(Raw_Data!$I$2:$I$44,Raw_Data!$C$2:$C$44,A4)</f>
         <v>44</v>
       </c>
-      <c r="D4" s="18" t="n">
-        <f aca="false">SUMIFS(Raw_Data!$O$2:$O$44,Raw_Data!$C$2:$C$44,A4)</f>
-        <v>153831.61</v>
-      </c>
-      <c r="E4" s="18" t="n">
-        <f aca="false">SUMIFS(Raw_Data!$P$2:$P$44,Raw_Data!$C$2:$C$44,A4)</f>
+      <c r="D4" s="19">
+        <f>SUMIFS(Raw_Data!$O$2:$O$44,Raw_Data!$C$2:$C$44,A4)</f>
+        <v>153831.60999999999</v>
+      </c>
+      <c r="E4" s="19">
+        <f>SUMIFS(Raw_Data!$P$2:$P$44,Raw_Data!$C$2:$C$44,A4)</f>
         <v>5647.53</v>
       </c>
-      <c r="F4" s="24" t="n">
-        <f aca="false">IFERROR(C4/(B4+C4),0)</f>
-        <v>0.0464135021097046</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F4" s="24">
+        <f t="shared" si="0"/>
+        <v>4.6413502109704644E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="B5" s="17" t="n">
-        <f aca="false">SUMIFS(Raw_Data!$H$2:$H$44,Raw_Data!$C$2:$C$44,A5)</f>
+      <c r="B5" s="18">
+        <f>SUMIFS(Raw_Data!$H$2:$H$44,Raw_Data!$C$2:$C$44,A5)</f>
         <v>808</v>
       </c>
-      <c r="C5" s="17" t="n">
-        <f aca="false">SUMIFS(Raw_Data!$I$2:$I$44,Raw_Data!$C$2:$C$44,A5)</f>
+      <c r="C5" s="18">
+        <f>SUMIFS(Raw_Data!$I$2:$I$44,Raw_Data!$C$2:$C$44,A5)</f>
         <v>42</v>
       </c>
-      <c r="D5" s="18" t="n">
-        <f aca="false">SUMIFS(Raw_Data!$O$2:$O$44,Raw_Data!$C$2:$C$44,A5)</f>
+      <c r="D5" s="19">
+        <f>SUMIFS(Raw_Data!$O$2:$O$44,Raw_Data!$C$2:$C$44,A5)</f>
         <v>141758.72</v>
       </c>
-      <c r="E5" s="18" t="n">
-        <f aca="false">SUMIFS(Raw_Data!$P$2:$P$44,Raw_Data!$C$2:$C$44,A5)</f>
-        <v>6025.84</v>
-      </c>
-      <c r="F5" s="24" t="n">
-        <f aca="false">IFERROR(C5/(B5+C5),0)</f>
-        <v>0.0494117647058824</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E5" s="19">
+        <f>SUMIFS(Raw_Data!$P$2:$P$44,Raw_Data!$C$2:$C$44,A5)</f>
+        <v>6025.8400000000011</v>
+      </c>
+      <c r="F5" s="24">
+        <f t="shared" si="0"/>
+        <v>4.9411764705882349E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="B6" s="17" t="n">
-        <f aca="false">SUMIFS(Raw_Data!$H$2:$H$44,Raw_Data!$C$2:$C$44,A6)</f>
+      <c r="B6" s="18">
+        <f>SUMIFS(Raw_Data!$H$2:$H$44,Raw_Data!$C$2:$C$44,A6)</f>
         <v>886</v>
       </c>
-      <c r="C6" s="17" t="n">
-        <f aca="false">SUMIFS(Raw_Data!$I$2:$I$44,Raw_Data!$C$2:$C$44,A6)</f>
+      <c r="C6" s="18">
+        <f>SUMIFS(Raw_Data!$I$2:$I$44,Raw_Data!$C$2:$C$44,A6)</f>
         <v>43</v>
       </c>
-      <c r="D6" s="18" t="n">
-        <f aca="false">SUMIFS(Raw_Data!$O$2:$O$44,Raw_Data!$C$2:$C$44,A6)</f>
-        <v>207809.5</v>
-      </c>
-      <c r="E6" s="18" t="n">
-        <f aca="false">SUMIFS(Raw_Data!$P$2:$P$44,Raw_Data!$C$2:$C$44,A6)</f>
-        <v>8465.41</v>
-      </c>
-      <c r="F6" s="24" t="n">
-        <f aca="false">IFERROR(C6/(B6+C6),0)</f>
-        <v>0.046286329386437</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D6" s="19">
+        <f>SUMIFS(Raw_Data!$O$2:$O$44,Raw_Data!$C$2:$C$44,A6)</f>
+        <v>207809.50000000003</v>
+      </c>
+      <c r="E6" s="19">
+        <f>SUMIFS(Raw_Data!$P$2:$P$44,Raw_Data!$C$2:$C$44,A6)</f>
+        <v>8465.4100000000017</v>
+      </c>
+      <c r="F6" s="24">
+        <f t="shared" si="0"/>
+        <v>4.6286329386437029E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="B7" s="17" t="n">
-        <f aca="false">SUMIFS(Raw_Data!$H$2:$H$44,Raw_Data!$C$2:$C$44,A7)</f>
+      <c r="B7" s="18">
+        <f>SUMIFS(Raw_Data!$H$2:$H$44,Raw_Data!$C$2:$C$44,A7)</f>
         <v>599</v>
       </c>
-      <c r="C7" s="17" t="n">
-        <f aca="false">SUMIFS(Raw_Data!$I$2:$I$44,Raw_Data!$C$2:$C$44,A7)</f>
+      <c r="C7" s="18">
+        <f>SUMIFS(Raw_Data!$I$2:$I$44,Raw_Data!$C$2:$C$44,A7)</f>
         <v>17</v>
       </c>
-      <c r="D7" s="18" t="n">
-        <f aca="false">SUMIFS(Raw_Data!$O$2:$O$44,Raw_Data!$C$2:$C$44,A7)</f>
+      <c r="D7" s="19">
+        <f>SUMIFS(Raw_Data!$O$2:$O$44,Raw_Data!$C$2:$C$44,A7)</f>
         <v>218251.75</v>
       </c>
-      <c r="E7" s="18" t="n">
-        <f aca="false">SUMIFS(Raw_Data!$P$2:$P$44,Raw_Data!$C$2:$C$44,A7)</f>
-        <v>5016.65</v>
-      </c>
-      <c r="F7" s="24" t="n">
-        <f aca="false">IFERROR(C7/(B7+C7),0)</f>
-        <v>0.0275974025974026</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E7" s="19">
+        <f>SUMIFS(Raw_Data!$P$2:$P$44,Raw_Data!$C$2:$C$44,A7)</f>
+        <v>5016.6499999999996</v>
+      </c>
+      <c r="F7" s="24">
+        <f t="shared" si="0"/>
+        <v>2.7597402597402596E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="26" t="s">
         <v>100</v>
       </c>
-      <c r="B8" s="26" t="n">
-        <f aca="false">SUM(B2:B7)</f>
+      <c r="B8" s="26">
+        <f>SUM(B2:B7)</f>
         <v>4681</v>
       </c>
-      <c r="C8" s="26" t="n">
-        <f aca="false">SUM(C2:C7)</f>
+      <c r="C8" s="26">
+        <f>SUM(C2:C7)</f>
         <v>320</v>
       </c>
-      <c r="D8" s="27" t="n">
-        <f aca="false">SUM(D2:D7)</f>
+      <c r="D8" s="27">
+        <f>SUM(D2:D7)</f>
         <v>1079244.71</v>
       </c>
-      <c r="E8" s="27" t="n">
-        <f aca="false">SUM(E2:E7)</f>
-        <v>53446.52</v>
-      </c>
-      <c r="F8" s="28" t="n">
-        <f aca="false">IFERROR(C8/(B8+C8),0)</f>
-        <v>0.0639872025594881</v>
+      <c r="E8" s="27">
+        <f>SUM(E2:E7)</f>
+        <v>53446.520000000004</v>
+      </c>
+      <c r="F8" s="28">
+        <f t="shared" si="0"/>
+        <v>6.3987202559488102E-2</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>